--- a/input/mapping/009. OCB_GOLD_TCKH_V_CUST_STATUS_NEW_BAOANH.xlsx
+++ b/input/mapping/009. OCB_GOLD_TCKH_V_CUST_STATUS_NEW_BAOANH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/ANHPB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1784" documentId="13_ncr:1_{65A8DFCB-4547-420A-82EC-B4C57912D235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33BDEF01-D278-49A9-8686-F667609864EF}"/>
+  <xr:revisionPtr revIDLastSave="1807" documentId="13_ncr:1_{65A8DFCB-4547-420A-82EC-B4C57912D235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9558EFCE-4D33-4DA4-B2AF-D06EBBAF504F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{D1E0AC4A-EE92-4A85-8B4C-1D02E566321C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="244">
   <si>
     <t>V_CUST_STATUS_NEW  —  Data Lineage Mind Map</t>
   </si>
@@ -252,20 +252,43 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
--- Ngày ETL nhận từ param :DATADT (job truyền vào, định dạng yyyyMMdd).
--- Dùng to_date(:DATADT, 'yyyyMMdd') inline ở mọi chỗ.
--- Daily snapshot trên Liquid Clustering: REPLACE WHERE chỉ thay thế đúng
--- lát cắt DATA_DT của ngày ETL (atomic, idempotent khi re-run cùng ngày),
+CREATE TABLE IF NOT EXISTS CST_LCS_KT_30D_FINAL_CASE5 (
+    DATA_DT                 DATE,
+    CIF                     DECIMAL(10,0),
+    T_COMPANY_BOOK          STRING,
+    T_CREATE_DATE           DATE NOT NULL,
+    FINAL_STATUS            STRING,
+    SCTR                    DECIMAL(10,0),
+    T_DESCRIPTION           STRING,
+    CST_GRP                 STRING,
+    CUST_GROUP_NAME         STRING,
+    CUST_GROUP_LINE         STRING,
+    CUST_GROUP_LINE_SHORT   STRING,
+    TIENGUI                 DECIMAL(20,4),
+    TIENVAY                 DECIMAL(20,4),
+    CUST_CURRENT_ACCT_A1    DECIMAL(20,4),
+    CIF_LOANCLASS            DECIMAL(3,0),
+    DOANHSO_BAOLANH_30D     DECIMAL(31,4),
+    DOANHSO_LC_30D          DECIMAL(31,4),
+    NUM_TRANS               INT,
+    ACTIVE_INDEX            INT,
+    T24_STATUS              STRING,
+    T24_ACTIVE_RB           INT,
+    T24_ACTIVE_COMB         INT,
+    T24_ACTIVE_TRE          INT,
+    T24_ACTIVE_CIB          INT,
+    T24_ACTIVE_CMB          INT,
+    T24_ACTIVE_DCTC         INT,
+    T24_ACTIVE_LIO          INT,
+    W4_STATUS               STRING,
+    W4_ACTIVE_RB            INT,
+    W4_ACTIVE_LIO           INT,
+    DATE_SYS                TIMESTAMP
+)
+USING DELTA;
 INSERT INTO CST_LCS_KT_30D_FINAL_CASE5
 REPLACE WHERE DATA_DT = to_date(:DATADT, 'yyyyMMdd')
 WITH
--- =========================================================================
--- STS_DEL / ACTIVE theo template chuẩn: &lt;ent&gt;_sts_del chỉ chứa hashkey có
--- trạng thái mới nhất (&lt;= DATADT) = 'D'; &lt;ent&gt;_active = Hub LEFT JOIN
--- &lt;ent&gt;_sts_del rồi loại các hashkey khớp (WHERE ... IS NULL). Đúng chuẩn
--- Data Vault: (1) delete phát sinh SAU DATADT không ảnh hưởng snapshot quá
--- khứ; (2) key bị xóa rồi tái tạo (D -&gt; I/U &lt;= DATADT) KHÔNG bị loại nhầm.
--- =========================================================================
 cte_customer_sts_del AS (
     SELECT customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_customer')
@@ -273,13 +296,6 @@
     GROUP BY customer_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
-cte_customer_active AS (
-    SELECT h.customer_hashkey, h.business_key, h.source_event_date
-    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_customer') h
-    LEFT JOIN cte_customer_sts_del d ON d.customer_hashkey = h.customer_hashkey
-    WHERE h.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
-      AND d.customer_hashkey IS NULL
-),
 cte_account_sts_del AS (
     SELECT account_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_account')
@@ -301,11 +317,68 @@
     GROUP BY md_deal_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
--- =========================================================================
--- 0. TRỤC CHÍNH: hub_customer, loại customer đã bị xóa (cte_customer_sts_del
---    qua cte_customer_active). Dedup theo customer_hashkey (giá trị max_by
---    theo source_event_date lớn nhất, giữ nguyên như bản gốc).
--- =========================================================================
+-- ===== Rule 2.12: snapshot mỗi bảng Silver đọc nhiều nơi thành 1 CTE duy nhất =====
+cte_snap_hub_customer AS (
+    SELECT customer_hashkey, business_key, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_customer')
+),
+cte_customer_active AS (
+    SELECT h.customer_hashkey, h.business_key, h.source_event_date
+    FROM cte_snap_hub_customer h
+    LEFT JOIN cte_customer_sts_del d ON d.customer_hashkey = h.customer_hashkey
+    WHERE h.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+      AND d.customer_hashkey IS NULL
+),
+cte_snap_hub_branch AS (
+    SELECT branch_hashkey, business_key
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch')
+),
+cte_snap_hub_account AS (
+    SELECT account_hashkey, business_key
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_account')
+),
+cte_snap_link_account_customer AS (
+    SELECT customer_hashkey, account_hashkey, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_customer')
+),
+cte_snap_link_crb_account AS (
+    SELECT account_hashkey, crb_hashkey, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_crb_account')
+),
+cte_snap_hub_crb AS (
+    SELECT crb_hashkey, gl, tieukhoan
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_crb')
+),
+cte_snap_link_letter_of_credit_customer AS (
+    SELECT customer_hashkey, letter_of_credit_hashkey, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_letter_of_credit_customer')
+),
+cte_snap_sat_account_balance AS (
+    SELECT account_hashkey, t_open_actual_bal, t_currency, source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_account_balance')
+    WHERE source_event_date = to_date(:DATADT, 'yyyyMMdd')
+),
+-- ===== Rule X.1: rút link về current (1 dòng / driving key) trước khi join, chống fan-out =====
+cte_link_crb_account_cur AS (
+    SELECT
+        account_hashkey,
+        max_by(crb_hashkey, source_event_date) AS crb_hashkey
+    FROM cte_snap_link_crb_account
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY account_hashkey
+),
+cte_link_md_deal_customer_cur AS (
+    SELECT
+        md_deal_hashkey,
+        max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_md_deal_customer')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY md_deal_hashkey
+),
+cte_snap_calendar AS (
+    SELECT msr_prd_id, bsn_day_f
+    FROM IDENTIFIER(:cleaned || '.business_vault.calendar')
+),
 base_customer AS (
     SELECT
         h.customer_hashkey,
@@ -314,24 +387,16 @@
     FROM cte_customer_active h
     GROUP BY h.customer_hashkey
 ),
--- =========================================================================
--- 3. T_COMPANY_BOOK: link_customer_branch -&gt; hub_branch.business_key
---    Dedup theo customer_hashkey (giữ branch mới nhất) bằng MAX_BY.
--- =========================================================================
 cte_company_book AS (
     SELECT
         lcb.customer_hashkey,
         max_by(hb.business_key, lcb.source_event_date) AS t_company_book
     FROM IDENTIFIER(:cleaned || '.raw_vault.link_customer_branch') lcb
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_branch') hb
+    JOIN cte_snap_hub_branch hb
       ON hb.branch_hashkey = lcb.branch_hashkey
+    WHERE lcb.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY lcb.customer_hashkey
 ),
--- =========================================================================
--- 4. T_CREATE_DATE: NVL(sat_customer_information.T_CREATE_DATE,
---                       hub_customer.source_event_date)
---    Lọc sat: max(source_event_date) &lt;= [ETL]. Dedup theo customer_hashkey.
--- =========================================================================
 cte_create_date AS (
     SELECT
         sci.customer_hashkey,
@@ -340,11 +405,6 @@
     WHERE sci.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY sci.customer_hashkey
 ),
--- =========================================================================
--- 6,8,15. sat_customer_classification: SCTR, CST_GRP, CIF_LOANCLASS
---    Gộp chung vì cùng 1 satellite, cùng điều kiện lọc/dedup.
---    Lọc sat: max(source_event_date) &lt;= [ETL]. Dedup theo customer_hashkey.
--- =========================================================================
 cte_customer_classification AS (
     SELECT
         scl.customer_hashkey,
@@ -355,35 +415,20 @@
     WHERE scl.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY scl.customer_hashkey
 ),
--- =========================================================================
--- 7. T_DESCRIPTION: ref_t24_sector theo ref_code = scl.sector
---    Dedup theo ref_code. LƯU Ý: bảng ref này không có source_event_date
---    trong nguồn gốc (dùng ORDER BY chính ref_code làm cột dedup arbitrary
---    trong bản cũ). Giữ nguyên hành vi arbitrary-pick-1-dòng/ref_code bằng
---    MAX(ref_description) — nếu ref_t24_sector thực có source_event_date,
---    cần đổi lại thành GROUP BY ref_code + MAX_BY(ref_description, source_event_date).
--- =========================================================================
 cte_sector_desc AS (
     SELECT
         rts.ref_code,
-        MAX(rts.ref_description) AS t_description
+        max_by(rts.ref_description, rts.source_event_date) AS t_description
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_sector') rts
+    WHERE rts.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY rts.ref_code
 ),
--- =========================================================================
--- 9. CUST_GROUP_NAME: ref_t24_ocbh_cus_group.ref_description
---    theo ref_code = scl.cust_group. Dedup theo ref_code (cùng lưu ý như
---    cte_sector_desc ở trên).
--- 10,11. CUST_GROUP_LINE / CUST_GROUP_LINE_SHORT: bảng danh mục mnl_ocbh_cust_group
---    (gold layer, catalog :curated, schema tckh -- cùng cơ chế upload thủ công
---    như gl_param/mnl_card_pln_out), join theo custgroup_id = cst_grp và
---    data_date = ngày ETL.
--- =========================================================================
 cte_cust_group AS (
     SELECT
         ocg.ref_code,
-        MAX(ocg.ref_description) AS cust_group_name   -- cột 9
+        max_by(ocg.ref_description, ocg.source_event_date) AS cust_group_name   -- cột 9
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_ocbh_cus_group') ocg
+    WHERE ocg.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ocg.ref_code
 ),
 cte_mnl_cust_group AS (
@@ -394,12 +439,6 @@
     FROM IDENTIFIER(:curated || '.tckh.mnl_ocbh_cust_group')
     -- WHERE data_date = to_date(:DATADT, 'yyyyMMdd')
 ),
--- =========================================================================
--- 12,13. TIENGUI / TIENVAY: business_vault.csat_customer_sum_balance
---    Lọc: max(source_event_date) &lt;= [ETL]. Dedup theo customer_hashkey.
---    Lấy kèm so_du_bao_lanh/so_du_lc (cùng bảng) để tính BAOLANH_LC cho
---    T24_STATUS bên dưới (BAOLANH_LC = SO_DU_BAO_LANH + SO_DU_LC).
--- =========================================================================
 cte_customer_balance AS (
     SELECT
         ccb.customer_hashkey,
@@ -411,20 +450,6 @@
     WHERE ccb.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ccb.customer_hashkey
 ),
--- =========================================================================
--- 14. CUST_CURRENT_ACCT_A1  (số dư TK thanh toán KKH - TGTT1KKH)
---    Theo mapping (4 bước, tầng Data Vault):
---    B1: account gắn CIF qua link_account_customer -&gt; hub_account
---        + sat_account_balance (t_currency), sat_account_classification
---          (t_condition_group), ref_t24_acct_group_condition (t_minimum_bal).
---    B2: chỉ giữ TK thanh toán (GL_TYPE 'TGTT1KKH'), loại GL tiết kiệm KKH/
---        tiền gửi/ký quỹ; số dư &gt;= mức tối thiểu.
---    B3: bổ sung TK số dư = 0 thỏa mức tối thiểu, chưa có ở B2.
---    B4: UNION B2 + B3, SUM theo customer_hashkey.
---    Dedup: SUM đã group theo customer_hashkey nên 1 dòng/CIF.
---    Loại account đã xóa qua cte_account_sts_del (LEFT JOIN ... IS NULL,
---    thay cho NOT EXISTS — kết quả tập account active giữ nguyên).
--- =========================================================================
 cte_acct_base AS (   -- Bước 1
     SELECT
         lac.customer_hashkey,
@@ -433,8 +458,8 @@
         max_by(sab.t_currency,        lac.source_event_date) AS t_currency,
         max_by(sac.t_condition_group, lac.source_event_date) AS t_condition_group,
         max_by(mini.t_minimum_bal,    lac.source_event_date) AS t_minimum_bal
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_customer') lac
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account') ha
+    FROM cte_snap_link_account_customer lac
+    JOIN cte_snap_hub_account ha
       ON ha.account_hashkey = lac.account_hashkey
     LEFT JOIN cte_account_sts_del d_acc
       ON d_acc.account_hashkey = ha.account_hashkey
@@ -443,8 +468,7 @@
             account_hashkey,
             max_by(t_open_actual_bal, source_event_date) AS t_open_actual_bal,
             max_by(t_currency,        source_event_date) AS t_currency
-        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_account_balance')
-        WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+        FROM cte_snap_sat_account_balance
         GROUP BY account_hashkey
     ) sab ON sab.account_hashkey = ha.account_hashkey
     LEFT JOIN (
@@ -458,20 +482,17 @@
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_t24_acct_group_condition') mini
       ON mini.id = CONCAT(sac.t_condition_group, sab.t_currency)
     WHERE d_acc.account_hashkey IS NULL
-    -- lọc link_account_customer: giữ nguyên như bản gốc (không có
-    -- WHERE lac.source_event_date &lt;= [ETL] tường minh trong code cũ dù comment
-    -- có ghi; KHÔNG bổ sung ở đây theo đúng yêu cầu giữ nguyên logic)
     GROUP BY lac.customer_hashkey, lac.account_hashkey
 ),
-cte_acct_b2 AS (    -- Bước 2: TK thanh toán, số dư &gt;= mức tối thiểu
+cte_acct_b2 AS (    
     SELECT
         lca.account_hashkey,
         max_by(b.customer_hashkey,  lca.source_event_date) AS customer_hashkey,
         max_by(b.t_open_actual_bal, lca.source_event_date) AS t_open_actual_bal
     FROM cte_acct_base b
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.link_crb_account') lca
+    JOIN cte_link_crb_account_cur lca
       ON lca.account_hashkey = b.account_hashkey
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_crb') hcrb
+    JOIN cte_snap_hub_crb hcrb
       ON hcrb.crb_hashkey = lca.crb_hashkey
     LEFT JOIN cte_crb_sts_del d_crb
       ON d_crb.crb_hashkey = hcrb.crb_hashkey
@@ -494,7 +515,7 @@
       AND NVL(b.t_open_actual_bal, 0) = 0
       AND b.account_hashkey NOT IN (SELECT account_hashkey FROM cte_acct_b2)
 ),
-cte_cust_current_acct_a1 AS (   -- Bước 4: UNION + SUM theo CIF
+cte_cust_current_acct_a1 AS (   
     SELECT
         customer_hashkey,
         CAST(SUM(NVL(ABS(t_open_actual_bal), 0)) AS DECIMAL(20,4)) AS cust_current_acct_a1
@@ -505,19 +526,13 @@
     )
     GROUP BY customer_hashkey
 ),
--- =========================================================================
--- TOL_BAL_CUST_A3 (không xuất cột, chỉ dùng cho T24_STATUS/IsActive):
---    SUM số dư TK thuộc nhóm GL tiết kiệm KKH/tiền gửi/ký quỹ (14 mã GL) --
---    cùng danh sách GL bị loại trừ khỏi CUST_CURRENT_ACCT_A1 ở trên.
---    Loại account/crb đã xóa qua cte_account_sts_del / cte_crb_sts_del.
--- =========================================================================
 cte_tol_bal_a3_base AS (
     SELECT
         lac.customer_hashkey,
         lac.account_hashkey,
         max_by(sab.t_open_actual_bal, lac.source_event_date) AS t_open_actual_bal
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_customer') lac
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account') ha
+    FROM cte_snap_link_account_customer lac
+    JOIN cte_snap_hub_account ha
       ON ha.account_hashkey = lac.account_hashkey
     LEFT JOIN cte_account_sts_del d_acc
       ON d_acc.account_hashkey = ha.account_hashkey
@@ -525,13 +540,12 @@
         SELECT
             account_hashkey,
             max_by(t_open_actual_bal, source_event_date) AS t_open_actual_bal
-        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_account_balance')
-        WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+        FROM cte_snap_sat_account_balance
         GROUP BY account_hashkey
     ) sab ON sab.account_hashkey = ha.account_hashkey
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.link_crb_account') lca
+    JOIN cte_link_crb_account_cur lca
       ON lca.account_hashkey = ha.account_hashkey
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_crb') hcrb
+    JOIN cte_snap_hub_crb hcrb
       ON hcrb.crb_hashkey = lca.crb_hashkey
     LEFT JOIN cte_crb_sts_del d_crb
       ON d_crb.crb_hashkey = hcrb.crb_hashkey
@@ -547,12 +561,7 @@
     FROM cte_tol_bal_a3_base
     GROUP BY customer_hashkey
 ),
--- =========================================================================
--- 16. DOANHSO_BAOLANH_30D: SUM số dư hợp đồng bảo lãnh theo KH (value_date 30D)
---    Theo mapping (3 bước). Dedup ở output cuối bằng GROUP BY customer_hashkey.
---    Loại md_deal đã xóa qua cte_md_deal_sts_del.
--- =========================================================================
-cte_md_30d AS (     -- Bước 1: HĐ có value_date trong 30 ngày
+cte_md_30d AS (     
     SELECT
         smdi.md_deal_hashkey,
         max_by(smdi.t_value_date, smdi.source_event_date) AS value_date
@@ -564,36 +573,32 @@
       AND d_md.md_deal_hashkey IS NULL
     GROUP BY smdi.md_deal_hashkey
 ),
-cte_md_b2 AS (      -- Bước 2: value_date = ngày làm việc (calendar), lấy số dư crb
+cte_md_b2 AS (      
     SELECT
         md1.md_deal_hashkey,
         scb.noite
     FROM cte_md_30d md1
-    JOIN IDENTIFIER(:cleaned || '.business_vault.calendar') cal
+    JOIN cte_snap_calendar cal
       ON md1.value_date = cal.msr_prd_id AND cal.bsn_day_f = 1
     JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_md_deal') hmd
       ON hmd.md_deal_hashkey = md1.md_deal_hashkey
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_crb') hcb
+    JOIN cte_snap_hub_crb hcb
       ON hcb.tieukhoan = hmd.business_key AND hcb.gl &lt;&gt; '9995'
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance') scb
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance') scb
       ON scb.crb_hashkey = hcb.crb_hashkey
      AND scb.ma_key BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
-),
-cte_doanhso_baolanh_30d AS (    -- Bước 3: SUM theo customer_hashkey
+     AND scb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
+),
+cte_doanhso_baolanh_30d AS (  
     SELECT
         lcif.customer_hashkey,
-        CAST(SUM(b2.noite) AS DECIMAL(31,4)) AS doanhso_baolanh_30d
+        CAST(SUM(NVL(b2.noite, 0)) AS DECIMAL(31,4)) AS doanhso_baolanh_30d
     FROM cte_md_b2 b2
-    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.link_md_deal_customer') lcif
+    LEFT JOIN cte_link_md_deal_customer_cur lcif
       ON lcif.md_deal_hashkey = b2.md_deal_hashkey
-     AND lcif.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY lcif.customer_hashkey
 ),
--- =========================================================================
--- 17. DOANHSO_LC_30D: SUM giá trị HĐ LC (applicant + beneficiary) theo CIF
---    Theo mapping (3 bước). Dedup ở output cuối bằng GROUP BY customer_hashkey.
--- =========================================================================
-cte_lc_30d AS (     -- Bước 1: LC phát hành mới trong 30 ngày
+cte_lc_30d AS (    
     SELECT
         slct.letter_of_credit_hashkey,
         max_by(slct.t_issue_date, slct.source_event_date) AS t_issue_date
@@ -602,38 +607,42 @@
       AND slct.t_issue_date BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
     GROUP BY slct.letter_of_credit_hashkey
 ),
-cte_lc_value AS (   -- giá trị LC (min amount, currency)
+cte_lc_value AS (  
     SELECT
         lc.letter_of_credit_hashkey,
         MIN(lc.t_issue_date)     AS issue_date,
         MIN(slcv.t_lc_amount)    AS first_lc_amount,
         slcv.t_lc_currency
     FROM cte_lc_30d lc
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_value') slcv
+    LEFT JOIN (
+        SELECT
+            letter_of_credit_hashkey,
+            max_by(t_lc_amount,   source_event_date) AS t_lc_amount,
+            max_by(t_lc_currency, source_event_date) AS t_lc_currency
+        FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_value')
+        WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+        GROUP BY letter_of_credit_hashkey
+    ) slcv
       ON slcv.letter_of_credit_hashkey = lc.letter_of_credit_hashkey
     GROUP BY lc.letter_of_credit_hashkey, slcv.t_lc_currency
 ),
-cte_lc_customer AS ( -- Bước 2: applicant UNION ALL beneficiary
-    -- 2.1 Applicant
+cte_lc_customer AS ( 
     SELECT
         llcc.customer_hashkey,
         llcc.letter_of_credit_hashkey
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_letter_of_credit_customer') llcc
+    FROM cte_snap_link_letter_of_credit_customer llcc
     WHERE llcc.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     UNION ALL
-    -- 2.2 Beneficiary (giữ nguyên join thẳng hub_customer như bản gốc,
-    -- không qua base_customer/cte_customer_active theo đúng yêu cầu không
-    -- đổi logic — đã lưu ý riêng ở các lượt trước, KHÔNG sửa ở đây)
     SELECT
         hc.customer_hashkey,
         prt.letter_of_credit_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_party') prt
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_customer') hc
+    JOIN cte_snap_hub_customer hc
       ON hc.business_key = prt.t_beneficiary_custno
     WHERE prt.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
       AND prt.t_beneficiary_custno IS NOT NULL
 ),
-cte_doanhso_lc_30d AS (     -- Bước 3: quy đổi tỷ giá, SUM theo CIF
+cte_doanhso_lc_30d AS (   
     SELECT
         cust.customer_hashkey,
         CAST(SUM(
@@ -641,7 +650,7 @@
             NVL(CAST(REGEXP_EXTRACT(rc.t_mid_reval_rate, '[^:]+', 0) AS DECIMAL(20,8)), 0)
         ) AS DECIMAL(31,4)) AS doanhso_lc_30d
     FROM cte_lc_value v
-    JOIN IDENTIFIER(:cleaned || '.business_vault.calendar') cal
+    JOIN cte_snap_calendar cal
       ON v.issue_date = cal.msr_prd_id AND cal.bsn_day_f = 1
     JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_currency') rc
       ON rc.id = v.t_lc_currency
@@ -651,29 +660,11 @@
       ON cust.letter_of_credit_hashkey = v.letter_of_credit_hashkey
     GROUP BY cust.customer_hashkey
 ),
--- =========================================================================
--- 18. NUM_TRANS: đếm số bút toán 30D/90D từ hub_stmt_entry + hub_categ_entry.
---    (Giữ nguyên: cte_link_account_customer_cur ở đây KHÔNG loại account đã
---    xóa, đúng như bản gốc — không bổ sung anti-join theo yêu cầu không đổi
---    logic.)
---    Loại: business_key like 'F%', transaction_code = 381, inputter chứa
---    '_COB' (đúng nguyên văn mapping: 1 dấu gạch dưới trước COB, không có
---    gạch dưới sau), bút toán trùng funds_transfer/teller đã bị đảo (REVE) hoặc
---    thuộc nhóm phí ACFx. Ghi CÓ (t_amount_lcy &lt; 0): đếm từng bút toán.
---    Ghi NỢ: KHÔNG đếm từng bút toán, mà GỘP (union) tổng ghi nợ cả 2 nguồn
---    stmt + categ theo CIF trong kỳ, nếu &gt; 100,000 thì cộng thêm đúng 1 giao
---    dịch (ngưỡng áp 1 lần trên tập gộp, đúng DataStage cũ trên PST_ENTR).
---    GIẢ ĐỊNH cần business xác nhận lại bằng dữ liệu mẫu:
---    (1) cách tách business_key dạng "PREFIX;N" lấy bản ghi N lớn nhất;
---    (2) cách cắt T_TRANS_REFERENCE trước dấu "\";
---    (3) pattern loại trừ input '_COB' (underscore là ký tự đại diện
---        trong LIKE nên đã escape thành literal).
--- =========================================================================
 cte_link_account_customer_cur AS (
     SELECT
         account_hashkey,
         max_by(customer_hashkey, source_event_date) AS customer_hashkey
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_customer')
+    FROM cte_snap_link_account_customer
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY account_hashkey
 ),
@@ -689,90 +680,94 @@
     SELECT
         letter_of_credit_hashkey,
         max_by(customer_hashkey, source_event_date) AS customer_hashkey
-    FROM IDENTIFIER(:cleaned || '.raw_vault.link_letter_of_credit_customer')
+    FROM cte_snap_link_letter_of_credit_customer
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY letter_of_credit_hashkey
 ),
-cte_ft_dedup AS (   -- funds_transfer: 1 dòng/prefix, giữ số thứ tự (";N") lớn nhất
+cte_ft_dedup AS (  
     SELECT
         max_by(hft.business_key,      TRY_CAST(split_part(hft.business_key, ';', 2) AS INT)) AS gd_id,
         max_by(fti.t_record_status,    TRY_CAST(split_part(hft.business_key, ';', 2) AS INT)) AS t_record_status,
         max_by(fti.t_transaction_type, TRY_CAST(split_part(hft.business_key, ';', 2) AS INT)) AS t_transaction_type
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_funds_transfer') hft
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_funds_transfer_information') fti
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_funds_transfer_information') fti
       ON fti.funds_transfer_hashkey = hft.funds_transfer_hashkey
+     AND fti.source_event_date = to_date(:DATADT, 'yyyyMMdd')
     GROUP BY split_part(hft.business_key, ';', 1)
 ),
-cte_tt_dedup AS (   -- teller: cùng quy tắc dedup theo prefix
+cte_tt_dedup AS (
     SELECT
         max_by(tt.business_key,     TRY_CAST(split_part(tt.business_key, ';', 2) AS INT)) AS gd_id,
         max_by(tti.t_record_status, TRY_CAST(split_part(tt.business_key, ';', 2) AS INT)) AS t_record_status
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_teller') tt
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_teller_information') tti
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_teller_information') tti
       ON tti.teller_hashkey = tt.teller_hashkey
+     AND tti.source_event_date = to_date(:DATADT, 'yyyyMMdd')
     GROUP BY split_part(tt.business_key, ';', 1)
 ),
-cte_reve_gd AS (    -- bút toán bị đảo (REVE) qua FT hoặc teller
+cte_reve_gd AS (  
     SELECT gd_id FROM cte_ft_dedup WHERE t_record_status = 'REVE'
     UNION
     SELECT gd_id FROM cte_tt_dedup WHERE t_record_status = 'REVE'
 ),
-cte_acfx_gd AS (    -- bút toán phí FT nhóm ACFx
+cte_acfx_gd AS (   
     SELECT gd_id FROM cte_ft_dedup
     WHERE t_transaction_type IN ('ACF3','ACF9','ACFN','ACF5','ACF6','ACF8','ACF7','ACF0','ACF2','ACF4','ACFS')
 ),
-cte_stmt_txn_base AS (    -- Bước 1: bút toán từ stmt_entry, gắn CIF qua tài khoản
+cte_stmt_txn_base AS (   
     SELECT
         lac.customer_hashkey,
         hst.source_event_date,
         info.t_amount_lcy
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_stmt_entry') hst
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_information') info
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_information') info
       ON info.stmt_entry_hashkey = hst.stmt_entry_hashkey
      AND info.source_event_date = hst.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_classification') cls1
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_classification') cls1
       ON cls1.stmt_entry_hashkey = hst.stmt_entry_hashkey
      AND cls1.source_event_date = hst.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_audit') ad1
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_audit') ad1
       ON ad1.stmt_entry_hashkey = hst.stmt_entry_hashkey
      AND ad1.source_event_date = hst.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account') ha
+    JOIN cte_snap_hub_account ha
       ON ha.business_key = info.t_account_number
     JOIN cte_link_account_customer_cur lac
       ON lac.account_hashkey = ha.account_hashkey
+    LEFT JOIN cte_reve_gd r ON r.gd_id = split_part(info.t_trans_reference, '\\', 1)
+    LEFT JOIN cte_acfx_gd a ON a.gd_id = split_part(info.t_trans_reference, '\\', 1)
     WHERE hst.source_event_date BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -90) AND to_date(:DATADT, 'yyyyMMdd')
       AND hst.business_key NOT LIKE 'F%'
       AND cls1.t_transaction_code &lt;&gt; 381
       AND (ad1.t_inputter IS NULL OR ad1.t_inputter NOT LIKE '%\\_COB%' ESCAPE '\\')
-      AND NOT EXISTS (SELECT 1 FROM cte_reve_gd r WHERE r.gd_id = split_part(info.t_trans_reference, '\\', 1))
-      AND NOT EXISTS (SELECT 1 FROM cte_acfx_gd a WHERE a.gd_id = split_part(info.t_trans_reference, '\\', 1))
+      AND r.gd_id IS NULL
+      AND a.gd_id IS NULL
 ),
 cte_stmt_txn_agg AS (
     SELECT
         customer_hashkey,
-        COUNT(CASE WHEN source_event_date &gt;= DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND t_amount_lcy &lt; 0 THEN 1 END) AS credit_cnt_30d,
-        COUNT(CASE WHEN t_amount_lcy &lt; 0 THEN 1 END) AS credit_cnt_90d,
-        SUM(CASE WHEN source_event_date &gt;= DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_30d,
+        COUNT(CASE WHEN DATEDIFF(to_date(:DATADT, 'yyyyMMdd'), source_event_date) &lt;= 30 AND t_amount_lcy &lt; 0 THEN 1 ELSE NULL END) AS credit_cnt_30d,
+        COUNT(CASE WHEN t_amount_lcy &lt; 0 THEN 1 ELSE NULL END) AS credit_cnt_90d,
+        SUM(CASE WHEN DATEDIFF(to_date(:DATADT, 'yyyyMMdd'), source_event_date) &lt;= 30 AND t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_30d,
         SUM(CASE WHEN t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_90d
     FROM cte_stmt_txn_base
     GROUP BY customer_hashkey
 ),
-cte_categ_txn_base AS (    -- Bước 2: bút toán từ categ_entry, gắn CIF qua account/loan/LC theo t_system_id
+cte_categ_txn_base AS ( 
     SELECT
         NVL(lac.customer_hashkey, NVL(llnc.customer_hashkey, llcc.customer_hashkey)) AS customer_hashkey,
         ce.source_event_date,
         info.t_amount_lcy
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_categ_entry') ce
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_information') info
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_information') info
       ON info.categ_entry_hashkey = ce.categ_entry_hashkey
      AND info.source_event_date = ce.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_classification') cls1
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_classification') cls1
       ON cls1.categ_entry_hashkey = ce.categ_entry_hashkey
      AND cls1.source_event_date = ce.source_event_date
-    JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_audit') ad1
+    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_categ_entry_audit') ad1
       ON ad1.categ_entry_hashkey = ce.categ_entry_hashkey
      AND ad1.source_event_date = ce.source_event_date
-    LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_account') ha
+    LEFT JOIN cte_snap_hub_account ha
       ON ha.business_key = CASE
             WHEN cls1.t_system_id = 'AC' AND LEFT(info.t_our_reference, 2) = 'AZ'
                 THEN SUBSTR(info.t_our_reference, 4, 16)
@@ -795,28 +790,27 @@
          END
     LEFT JOIN cte_link_lc_customer_cur llcc
       ON llcc.letter_of_credit_hashkey = hlc.letter_of_credit_hashkey
+    LEFT JOIN cte_reve_gd r ON r.gd_id = split_part(info.t_trans_reference, '\\', 1)
+    LEFT JOIN cte_acfx_gd a ON a.gd_id = split_part(info.t_trans_reference, '\\', 1)
     WHERE ce.source_event_date BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -90) AND to_date(:DATADT, 'yyyyMMdd')
       AND ce.business_key NOT LIKE 'F%'
       AND cls1.t_transaction_code &lt;&gt; 381
       AND (ad1.t_inputter IS NULL OR ad1.t_inputter NOT LIKE '%\\_COB%' ESCAPE '\\')
-      AND NOT EXISTS (SELECT 1 FROM cte_reve_gd r WHERE r.gd_id = split_part(info.t_trans_reference, '\\', 1))
-      AND NOT EXISTS (SELECT 1 FROM cte_acfx_gd a WHERE a.gd_id = split_part(info.t_trans_reference, '\\', 1))
+      AND r.gd_id IS NULL
+      AND a.gd_id IS NULL
       AND NVL(lac.customer_hashkey, NVL(llnc.customer_hashkey, llcc.customer_hashkey)) IS NOT NULL
 ),
 cte_categ_txn_agg AS (
     SELECT
         customer_hashkey,
-        COUNT(CASE WHEN source_event_date &gt;= DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND t_amount_lcy &lt; 0 THEN 1 END) AS credit_cnt_30d,
-        COUNT(CASE WHEN t_amount_lcy &lt; 0 THEN 1 END) AS credit_cnt_90d,
-        SUM(CASE WHEN source_event_date &gt;= DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_30d,
+        COUNT(CASE WHEN DATEDIFF(to_date(:DATADT, 'yyyyMMdd'), source_event_date) &lt;= 30 AND t_amount_lcy &lt; 0 THEN 1 ELSE NULL END) AS credit_cnt_30d,
+        COUNT(CASE WHEN t_amount_lcy &lt; 0 THEN 1 ELSE NULL END) AS credit_cnt_90d,
+        SUM(CASE WHEN DATEDIFF(to_date(:DATADT, 'yyyyMMdd'), source_event_date) &lt;= 30 AND t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_30d,
         SUM(CASE WHEN t_amount_lcy &gt;= 0 THEN t_amount_lcy ELSE 0 END) AS debit_sum_90d
     FROM cte_categ_txn_base
     GROUP BY customer_hashkey
 ),
-cte_num_trans AS (    -- Bước 3: GỘP (union) stmt + categ theo KH. Ghi CÓ (amount&lt;0):
-                      -- đếm từng bút toán, cộng count 2 nguồn. Ghi NỢ: GỘP tổng nợ
-                      -- cả 2 nguồn (= tổng trên tập union) rồi so ngưỡng &gt;100,000 CHỈ
-                      -- 1 lần -&gt; tối đa +1 (đúng DataStage cũ chạy trên PST_ENTR gộp).
+cte_num_trans AS (  
     SELECT
         COALESCE(s.customer_hashkey, c.customer_hashkey) AS customer_hashkey,
         NVL(s.credit_cnt_30d, 0) + NVL(c.credit_cnt_30d, 0)
@@ -827,33 +821,13 @@
     FULL OUTER JOIN cte_categ_txn_agg c
       ON c.customer_hashkey = s.customer_hashkey
 ),
--- =========================================================================
--- 20. T24_STATUS: tự tham chiếu chính bảng đích (CST_LCS_KT_30D_FINAL_CASE5)
---    của các ngày ETL trước đó để lấy NEW_CUST/NON_DORMANT.
---    QUAN TRỌNG - ràng buộc vận hành: job PHẢI chạy tuần tự theo đúng thứ tự
---    ngày (không backfill song song/ngoài thứ tự), vì kết quả ngày N phụ
---    thuộc FINAL_STATUS đã commit của (tối đa) 181 ngày trước đó.
---    (Giữ nguyên như bản gốc, kể cả việc cte_non_dormant bao gồm cả DATADT
---    đang chạy trong cận trên — đã lưu ý riêng ở lượt trước, KHÔNG sửa ở đây.)
---    Bước 1: NEW_CUST = 1 nếu ngày làm việc liền trước KHÔNG có bản ghi
---    final_status = 'ORIGINAL' cho CIF này; NON_DORMANT = số ngày trong 181
---    ngày gần nhất mà final_status KHÔNG thuộc ('DORMANT','LOST').
---    SRC_LCS_TP_ID = NEW_CUST=1 -&gt; 'ORIGINAL'; else NON_DORMANT&gt;0 -&gt; 'DORMANT'
---    (từng active gần đây nhưng không phải hôm nay); else 'LOST'.
---    Bước 2: IsActive theo nhánh CST_GRP[1,1], dùng TIENGUI, TOL_BAL_CUST_A3,
---    CUST_CURRENT_ACCT_A1 + NUM_TRANS, TIENVAY + CIF_LOANCLASS, và BAOLANH_LC
---    (= so_du_bao_lanh + so_du_lc, business_vault.csat_customer_sum_balance).
---    Bước 3: IsActive=1 -&gt; 'ACTIVE'; else SRC_LCS_TP_ID (nhánh
---    IsActive=0 AND SRC_LCS_TP_ID='ACTIVE' -&gt; 'DORMANT' không bao giờ khớp vì
---    SRC_LCS_TP_ID chỉ nhận ORIGINAL/DORMANT/LOST -- giữ lại để đúng mapping).
--- =========================================================================
-cte_prev_bsn_day AS (   -- ngày làm việc liền trước ETL_DATE
+cte_prev_bsn_day AS (   
     SELECT MAX(msr_prd_id) AS prev_bsn_day
-    FROM IDENTIFIER(:cleaned || '.business_vault.calendar')
+    FROM cte_snap_calendar
     WHERE bsn_day_f = 1
       AND msr_prd_id &lt; to_date(:DATADT, 'yyyyMMdd')
 ),
-cte_new_cust AS (   -- NEW_CUST: ngày làm việc trước KHÔNG có final_status = 'ORIGINAL'
+cte_new_cust AS (  
     SELECT bc.customer_hashkey
     FROM base_customer bc
     CROSS JOIN cte_prev_bsn_day pd
@@ -865,7 +839,7 @@
           AND prev.data_dt = pd.prev_bsn_day
     )
 ),
-cte_non_dormant AS (   -- NON_DORMANT: số ngày trong 181D gần nhất không DORMANT/LOST
+cte_non_dormant AS (  
     SELECT
         prev.cif,
         SUM(CASE WHEN prev.final_status NOT IN ('DORMANT', 'LOST') THEN 1 ELSE 0 END) AS non_dormant
@@ -882,7 +856,396 @@
             ELSE 'LOST'
         END AS src_lcs_tp_id
     FROM base_customer bc
-    LEF</t>
+    LEFT JOIN cte_new_cust nc ON nc.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_non_dormant nd ON nd.cif = bc.cif
+),
+cte_t24_status AS (
+    SELECT
+        bc.customer_hashkey,
+        CASE WHEN LEFT(cc.cst_grp, 1) IN ('1', '5') THEN
+            CASE
+                WHEN NVL(bal.tiengui, 0) &gt; 0 THEN 1
+                WHEN NVL(a3.tol_bal_cust_a3, 0) &gt; 0 THEN 1
+                WHEN NVL(a1.cust_current_acct_a1, 0) &gt;= 0 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 1
+                WHEN NVL(bal.tienvay, 0) &gt; 0 AND NVL(cc.cif_loanclass, 1) &lt;= 2 THEN 1
+                WHEN NVL(bal.tienvay, 0) &gt; 0 AND NVL(cc.cif_loanclass, 1) &gt; 2 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 1
+                WHEN NVL(bal.so_du_bao_lanh, 0) + NVL(bal.so_du_lc, 0) &gt; 0 THEN 1
+                ELSE 0
+            END
+        ELSE
+            CASE
+                WHEN NVL(bal.tiengui, 0) &gt; 0 THEN 1
+                WHEN NVL(a3.tol_bal_cust_a3, 0) &gt; 0 THEN 1
+                WHEN NVL(a1.cust_current_acct_a1, 0) &gt;= 0 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 1
+                WHEN NVL(bal.tienvay, 0) &gt; 0 AND NVL(cc.cif_loanclass, 1) &lt;= 2 THEN 1
+                WHEN NVL(bal.tienvay, 0) &gt; 0 AND NVL(cc.cif_loanclass, 1) &gt; 2 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 1
+                WHEN NVL(bal.so_du_bao_lanh, 0) + NVL(bal.so_du_lc, 0) &gt; 0 THEN 1
+                ELSE 0
+            END
+        END AS is_active,
+        st.src_lcs_tp_id
+    FROM base_customer bc
+    LEFT JOIN cte_customer_classification cc ON cc.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_customer_balance bal ON bal.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_tol_bal_a3 a3 ON a3.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_cust_current_acct_a1 a1 ON a1.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_num_trans nt ON nt.customer_hashkey = bc.customer_hashkey
+    LEFT JOIN cte_src_lcs_tp st ON st.customer_hashkey = bc.customer_hashkey
+),
+cte_t24_status_final AS (
+    SELECT
+        customer_hashkey,
+        CASE
+            WHEN is_active = 1 THEN 'ACTIVE'
+            WHEN is_active = 0 AND src_lcs_tp_id = 'ACTIVE' THEN 'DORMANT'
+            ELSE src_lcs_tp_id
+        END AS t24_status
+    FROM cte_t24_status
+),
+cte_ref_way4_contr_status_cur AS (
+    SELECT
+        id,
+        max_by(code, source_event_date) AS code
+    FROM IDENTIFIER(:cleaned || '.raw_vault.ref_way4_contr_status')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY id
+),
+cte_w4_acnt_contract_info_cur AS (   
+    SELECT
+        acnt_contract_hashkey,
+        max_by(contract_number, source_event_date) AS contract_number,
+        max_by(contr_status,    source_event_date) AS contr_status
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_acnt_contract_information')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),</t>
+  </si>
+  <si>
+    <t>cte_w4_acnt_contract_type_cur AS (   
+    SELECT
+        acnt_contract_hashkey,
+        max_by(con_cat,  source_event_date) AS con_cat,
+        max_by(ext_data, source_event_date) AS ext_data
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_acnt_contract_type')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),
+cte_w4_acnt_contract_branch_cur AS (
+    SELECT
+        acnt_contract_hashkey,
+        max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_acnt_contract_branch')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),
+cte_w4_acnt_contract_product_cur AS (
+    SELECT
+        acnt_contract_hashkey,
+        max_by(product_hashkey, source_event_date) AS product_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_acnt_contract_product')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),
+cte_w4_acnt_contract_client_cur AS (
+    SELECT
+        acnt_contract_hashkey,
+        max_by(client_hashkey, source_event_date) AS client_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_acnt_contract_client')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY acnt_contract_hashkey
+),
+cte_w4_link_acc_contract_card_active AS (
+    SELECT
+        lacc.card_hashkey,
+        lacc.account_contract_hashkey,
+        lacc.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_account_contract_card') lacc
+    WHERE lacc.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+),
+cte_w4_account_contract_card_cur AS (
+    SELECT
+        lacc.card_hashkey,
+        max_by(lacc.account_contract_hashkey, lacc.source_event_date) AS account_contract_hashkey
+    FROM cte_w4_link_acc_contract_card_active lacc
+    JOIN cte_w4_acnt_contract_type_cur cc
+      ON cc.acnt_contract_hashkey = lacc.card_hashkey
+     AND cc.con_cat = 'C'
+    GROUP BY lacc.card_hashkey
+),
+cte_w4_product_info_cur AS (
+    SELECT
+        product_hashkey,
+        max_by(code, source_event_date) AS code
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_product_information')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY product_hashkey
+),
+cte_w4_balance_link_cur AS (
+    SELECT
+        balance_hashkey,
+        max_by(acnt_contract_hashkey, source_event_date) AS acnt_contract_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_balance_acnt_contract')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY balance_hashkey
+),
+cte_w4_balance_info_cur AS (
+    SELECT
+        balance_hashkey,
+        max_by(savings_balance,        source_event_date) AS savings_balance,
+        max_by(fixed_term_balance,     source_event_date) AS fixed_term_balance,
+        max_by(flexible_term_balance,  source_event_date) AS flexible_term_balance,
+        max_by(total_balance,          source_event_date) AS total_balance
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_balance_information')
+    WHERE source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY balance_hashkey
+),
+cte_w4_balance_principal_cur AS (
+    SELECT
+        balance_hashkey,
+        max_by(principal_balance, source_event_date) AS principal_balance
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_balance_principal')
+    WHERE source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY balance_hashkey
+),
+cte_w4_balance_instalment_cur AS (
+    SELECT
+        balance_hashkey,
+        max_by(instalment_balance, source_event_date) AS instalment_balance
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_balance_instalment')
+    WHERE source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY balance_hashkey
+),
+cte_w4_client_customer_cur AS (
+    SELECT
+        client_hashkey,
+        max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_client_customer')
+    WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    GROUP BY client_hashkey
+),
+cte_w4_loan_class AS (   
+    SELECT so_hd, loan_class
+    FROM IDENTIFIER(:curated || '.tckh.mnl_card_pln_out')
+    WHERE ngay_du_lieu = to_date(:DATADT, 'yyyyMMdd')
+),
+cte_w4_card_contract AS (
+    SELECT
+        lac.acnt_contract_hashkey                          AS issuing_hashkey,
+        max_by(cc.acnt_contract_hashkey, cc.business_key)  AS card_hashkey,
+        max_by(sci.contract_number,      cc.business_key)  AS issuing_number,
+        max_by(br.business_key,          cc.business_key)  AS branch_code,
+        max_by(
+            CASE WHEN LOCATE('LAST_TRANS_DATE', sty.ext_data) &gt; 0 THEN
+                SUBSTR(sty.ext_data,
+                    LOCATE('LAST_TRANS_DATE', sty.ext_data) + 16,
+                    LOCATE(';', sty.ext_data, LOCATE('LAST_TRANS_DATE', sty.ext_data) + 16)
+                        - LOCATE('LAST_TRANS_DATE', sty.ext_data) - 16)
+            ELSE NULL END,
+            cc.business_key
+        ) AS last_trans_date
+    FROM cte_w4_account_contract_card_cur lacc
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_acnt_contract') cc
+      ON cc.acnt_contract_hashkey = lacc.card_hashkey
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_acnt_contract') lac
+      ON lac.acnt_contract_hashkey = lacc.account_contract_hashkey
+    JOIN cte_w4_acnt_contract_info_cur scc
+      ON scc.acnt_contract_hashkey = cc.acnt_contract_hashkey    -- thông tin thẻ
+    JOIN cte_w4_acnt_contract_info_cur sci
+      ON sci.acnt_contract_hashkey = lac.acnt_contract_hashkey   -- thông tin issuing (contract_number)
+    JOIN cte_w4_acnt_contract_type_cur sty
+      ON sty.acnt_contract_hashkey = cc.acnt_contract_hashkey
+     AND sty.con_cat = 'C'                                         -- card
+    JOIN cte_w4_acnt_contract_type_cur ity
+      ON ity.acnt_contract_hashkey = lac.acnt_contract_hashkey
+     AND ity.con_cat = 'A'                                         -- issuing
+    JOIN cte_w4_acnt_contract_branch_cur lbr
+      ON lbr.acnt_contract_hashkey = cc.acnt_contract_hashkey
+    JOIN cte_snap_hub_branch br
+      ON br.branch_hashkey = lbr.branch_hashkey
+    JOIN cte_w4_acnt_contract_product_cur lpr
+      ON lpr.acnt_contract_hashkey = cc.acnt_contract_hashkey
+    JOIN cte_w4_product_info_cur sp
+      ON sp.product_hashkey = lpr.product_hashkey
+    JOIN cte_ref_way4_contr_status_cur rcs_c
+      ON rcs_c.id = scc.contr_status
+    JOIN cte_ref_way4_contr_status_cur rcs_i
+      ON rcs_i.id = sci.contr_status
+    WHERE SUBSTR(sp.code, 5, 1) = 'M'
+      AND rcs_i.code NOT IN ('13', '12', '33')    -- Account Closed / Waiting Closed
+      AND rcs_c.code NOT IN ('14', '65', '05', '09', '54', '37', '41', '29')  -- Card Closed/Lost/Expired/...
+    GROUP BY lac.acnt_contract_hashkey
+),
+cte_w4_balance AS (   
+    SELECT
+        lba.acnt_contract_hashkey AS issuing_hashkey,
+        sbi.savings_balance,
+        sbi.fixed_term_balance,
+        sbi.flexible_term_balance,
+        sbi.total_balance,
+        sbp.principal_balance,
+        sbn.instalment_balance
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_balance') hb
+    JOIN cte_w4_balance_link_cur lba ON lba.balance_hashkey = hb.balance_hashkey
+    JOIN cte_w4_balance_info_cur sbi ON sbi.balance_hashkey = hb.balance_hashkey
+    JOIN cte_w4_balance_principal_cur sbp ON sbp.balance_hashkey = hb.balance_hashkey
+    JOIN cte_w4_balance_instalment_cur sbn ON sbn.balance_hashkey = hb.balance_hashkey
+),
+cte_w4_issuing_status AS ( 
+    SELECT
+        ci.card_hashkey,
+        ci.issuing_hashkey,
+        ci.branch_code,
+        CASE
+            WHEN (ci.credit_amount = 1 AND ci.trans_30d = 1)
+              OR (ci.debit_amount = 1 AND NVL(ci.loan_class, 1) &lt;= 2)
+              OR (ci.debit_amount = 1 AND NVL(ci.loan_class, 1) &gt; 2 AND ci.trans_30d = 1)
+              OR (ci.debit_amount = 0 AND ci.trans_30d = 1)
+              OR (ci.credit_amount = 0 AND ci.trans_30d = 1) THEN 1   -- ACTIVE
+            WHEN ci.trans_31_120d = 1 THEN 2                        -- DORMANT
+            WHEN ci.trans_121d = 1 THEN 3                           -- LOST
+            ELSE 4                                                  -- ORIGINAL
+        END AS issuing_status_id
+    FROM (
+        SELECT
+            base.card_hashkey,
+            base.issuing_hashkey,
+            base.branch_code,
+            lcls.loan_class,
+            CASE WHEN NVL(bl.savings_balance, 0) &gt; 0 OR NVL(bl.fixed_term_balance, 0) &gt; 0
+                  OR NVL(bl.flexible_term_balance, 0) &gt; 0 OR NVL(bl.total_balance, 0) &gt; 0
+                 THEN 1 ELSE 0 END AS credit_amount,
+            CASE WHEN NVL(bl.principal_balance, 0) + NVL(bl.instalment_balance, 0) &lt; 0
+                 THEN 1 ELSE 0 END AS debit_amount,
+            CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd')
+                       BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
+                 THEN 1 ELSE 0 END AS trans_30d,
+            CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd')
+                       BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180) AND DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -31)
+                 THEN 1 ELSE 0 END AS trans_31_120d,
+            CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd') &lt; DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180)
+                  AND base.last_trans_date &gt; '19000101'
+                 THEN 1 ELSE 0 END AS trans_121d
+        FROM cte_w4_card_contract base
+        LEFT JOIN cte_w4_balance bl ON bl.issuing_hashkey = base.issuing_hashkey
+        LEFT JOIN cte_w4_loan_class lcls ON lcls.so_hd = base.issuing_number
+    ) ci
+),
+cte_w4_branch_customer AS (   
+    SELECT
+        bc.customer_hashkey,
+        s.branch_code,
+        s.issuing_status_id
+    FROM cte_w4_issuing_status s
+    JOIN cte_w4_acnt_contract_client_cur lcl
+      ON lcl.acnt_contract_hashkey = s.card_hashkey
+    JOIN cte_w4_client_customer_cur lcc
+      ON lcc.client_hashkey = lcl.client_hashkey
+    JOIN base_customer bc
+      ON bc.customer_hashkey = lcc.customer_hashkey
+     AND bc.cif &lt;&gt; 'INSTANTCARD'
+),
+cte_w4_branch_min AS (  
+    SELECT
+        customer_hashkey,
+        branch_code,
+        MIN(issuing_status_id) AS min_issuing_status_id
+    FROM cte_w4_branch_customer
+    GROUP BY customer_hashkey, branch_code
+),
+cte_w4_status AS (  
+    SELECT
+        customer_hashkey,
+        CASE MIN(min_issuing_status_id)
+            WHEN 1 THEN 'ACTIVE'
+            WHEN 2 THEN 'DORMANT'
+            WHEN 3 THEN 'LOST'
+            WHEN 4 THEN 'ORIGINAL'
+            ELSE NULL
+        END AS w4_status,
+        MAX(CASE WHEN branch_code &lt;&gt; 'VN0010182' AND min_issuing_status_id = 1 THEN 1 ELSE 0 END) AS w4_active_rb,
+        MAX(CASE WHEN branch_code = 'VN0010182' AND min_issuing_status_id = 1 THEN 1 ELSE 0 END) AS w4_active_lio
+    FROM cte_w4_branch_min
+    GROUP BY customer_hashkey
+)
+SELECT
+    to_date(:DATADT, 'yyyyMMdd')                          AS DATA_DT,                 -- 1
+    bc.cif                                      AS CIF,                    -- 2
+    cb.t_company_book                           AS T_COMPANY_BOOK,         -- 3
+    NVL(cd.t_create_date, bc.hc_first_load_date) AS T_CREATE_DATE,         -- 4
+    CASE GREATEST(
+            CASE t24s.t24_status WHEN 'ACTIVE' THEN 4 WHEN 'DORMANT' THEN 3 WHEN 'LOST' THEN 2 WHEN 'ORIGINAL' THEN 1 ELSE -1 END,
+            CASE w4.w4_status    WHEN 'ACTIVE' THEN 4 WHEN 'DORMANT' THEN 3 WHEN 'LOST' THEN 2 WHEN 'ORIGINAL' THEN 1 ELSE -1 END
+         )
+        WHEN 4 THEN 'ACTIVE'
+        WHEN 3 THEN 'DORMANT'
+        WHEN 2 THEN 'LOST'
+        WHEN 1 THEN 'ORIGINAL'
+        ELSE NULL
+    END                                          AS FINAL_STATUS,
+    cc.sctr                                     AS SCTR,                   -- 6
+    sd.t_description                            AS T_DESCRIPTION,          -- 7
+    cc.cst_grp                                  AS CST_GRP,                -- 8
+    cg.cust_group_name                          AS CUST_GROUP_NAME,        -- 9
+    mcg.cust_group_line                         AS CUST_GROUP_LINE,        -- 10
+    mcg.cust_group_line_short                   AS CUST_GROUP_LINE_SHORT,  -- 11
+    NVL(bal.tiengui, 0)                         AS TIENGUI,                -- 12
+    NVL(bal.tienvay, 0)                         AS TIENVAY,                -- 13
+    NVL(a1.cust_current_acct_a1, 0)             AS CUST_CURRENT_ACCT_A1,   -- 14
+    cc.cif_loanclass                            AS CIF_LOANCLASS,          -- 15
+    NVL(md.doanhso_baolanh_30d, 0)              AS DOANHSO_BAOLANH_30D,    -- 16
+    NVL(lc.doanhso_lc_30d, 0)                   AS DOANHSO_LC_30D,         -- 17
+    CASE WHEN LEFT(cc.cst_grp, 1) IN ('1', '5')
+         THEN NVL(nt.num_trans_30d, 0)
+         ELSE NVL(nt.num_trans_90d, 0)
+    END                                          AS NUM_TRANS,
+    CASE WHEN LEFT(cc.cst_grp, 1) IN ('1', '5') THEN
+        CASE
+            WHEN NVL(bal.tiengui, 0) &gt; 0 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 1
+            WHEN NVL(a1.cust_current_acct_a1, 0) &gt; 0 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 2
+            WHEN NVL(bal.tienvay, 0) &gt; 0 AND cc.cif_loanclass = 1 THEN 3
+            WHEN NVL(bal.tienvay, 0) &gt; 0 AND cc.cif_loanclass &gt; 1 AND NVL(nt.num_trans_30d, 0) &gt; 0 THEN 4
+            WHEN NVL(md.doanhso_baolanh_30d, 0) &gt; 0 THEN 5
+            WHEN NVL(lc.doanhso_lc_30d, 0) &gt; 0 THEN 6
+            ELSE 0
+        END
+    ELSE
+        CASE
+            WHEN NVL(bal.tiengui, 0) &gt; 0 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 1
+            WHEN NVL(a1.cust_current_acct_a1, 0) &gt; 0 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 2
+            WHEN NVL(bal.tienvay, 0) &gt; 0 AND cc.cif_loanclass = 1 THEN 3
+            WHEN NVL(bal.tienvay, 0) &gt; 0 AND cc.cif_loanclass &gt; 1 AND NVL(nt.num_trans_90d, 0) &gt; 0 THEN 4
+            WHEN NVL(md.doanhso_baolanh_30d, 0) &gt; 0 THEN 5
+            WHEN NVL(lc.doanhso_lc_30d, 0) &gt; 0 THEN 6
+            ELSE 0
+        END
+    END                                         AS ACTIVE_INDEX,
+    t24s.t24_status                             AS T24_STATUS,
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'KRB' THEN 1 ELSE 0 END       AS T24_ACTIVE_RB,   -- 21
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'COMB' THEN 1 ELSE 0 END      AS T24_ACTIVE_COMB, -- 22
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'TREASURY' THEN 1 ELSE 0 END  AS T24_ACTIVE_TRE,  -- 23
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'CIB' THEN 1 ELSE 0 END       AS T24_ACTIVE_CIB,  -- 24
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'SME' THEN 1 ELSE 0 END       AS T24_ACTIVE_CMB,  -- 25
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'KDCTC' THEN 1 ELSE 0 END     AS T24_ACTIVE_DCTC, -- 26
+    CASE WHEN t24s.t24_status = 'ACTIVE' AND mcg.cust_group_line_short = 'LIOBANK' THEN 1 ELSE 0 END   AS T24_ACTIVE_LIO,  -- 27
+    w4.w4_status                                AS W4_STATUS,              -- 28
+    NVL(w4.w4_active_rb, 0)                     AS W4_ACTIVE_RB,           -- 29
+    NVL(w4.w4_active_lio, 0)                    AS W4_ACTIVE_LIO,          -- 30
+    NULL                                        AS DATE_SYS                -- 31
+FROM base_customer bc
+LEFT JOIN cte_company_book             cb  ON cb.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_create_date              cd  ON cd.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_customer_classification  cc  ON cc.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_sector_desc              sd  ON sd.ref_code          = cc.sctr
+LEFT JOIN cte_cust_group               cg  ON cg.ref_code          = cc.cst_grp
+LEFT JOIN cte_mnl_cust_group           mcg ON mcg.custgroup_id      = cc.cst_grp
+LEFT JOIN cte_customer_balance         bal ON bal.customer_hashkey = bc.customer_hashkey
+LEFT JOIN cte_cust_current_acct_a1     a1  ON a1.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_doanhso_baolanh_30d      md  ON md.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_doanhso_lc_30d           lc  ON lc.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_num_trans                nt  ON nt.customer_hashkey  = bc.customer_hashkey
+LEFT JOIN cte_t24_status_final         t24s ON t24s.customer_hashkey = bc.customer_hashkey
+LEFT JOIN cte_w4_status                w4  ON w4.customer_hashkey  = bc.customer_hashkey
+;</t>
   </si>
   <si>
     <t>V_CUST_STATUS_NEW — VIEW
@@ -3289,7 +3652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3413,81 +3776,81 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3503,9 +3866,45 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3514,45 +3913,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
@@ -3942,63 +4302,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="42" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
     </row>
     <row r="2" spans="1:11" ht="8.25" customHeight="1"/>
     <row r="3" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="D3" s="73" t="s">
+      <c r="B3" s="50"/>
+      <c r="D3" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="70"/>
+      <c r="E3" s="50"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="69" t="s">
+      <c r="G3" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="70"/>
-      <c r="J3" s="69" t="s">
+      <c r="H3" s="50"/>
+      <c r="J3" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="70"/>
+      <c r="K3" s="50"/>
     </row>
     <row r="4" spans="1:11" ht="8.25" customHeight="1">
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="51" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="52"/>
-      <c r="F5" s="50" t="s">
+      <c r="E5" s="72"/>
+      <c r="F5" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="G5" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="67"/>
-      <c r="I5" s="51" t="s">
+      <c r="H5" s="68"/>
+      <c r="I5" s="67" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="54" t="s">
@@ -4007,170 +4367,170 @@
       <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1">
-      <c r="A6" s="53"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="51"/>
+      <c r="A6" s="73"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="67"/>
       <c r="J6" s="56"/>
       <c r="K6" s="57"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
-      <c r="A7" s="53"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="51"/>
+      <c r="A7" s="73"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="67"/>
       <c r="J7" s="56"/>
       <c r="K7" s="57"/>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
-      <c r="A8" s="53"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="51"/>
+      <c r="A8" s="73"/>
+      <c r="B8" s="73"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="73"/>
+      <c r="F8" s="71"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="67"/>
       <c r="J8" s="56"/>
       <c r="K8" s="57"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A9" s="53"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="51"/>
+      <c r="A9" s="73"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="67"/>
       <c r="J9" s="56"/>
       <c r="K9" s="57"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A10" s="53"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="51"/>
+      <c r="A10" s="73"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="67"/>
       <c r="J10" s="56"/>
       <c r="K10" s="57"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A11" s="53"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="51"/>
+      <c r="A11" s="73"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="67"/>
       <c r="J11" s="56"/>
       <c r="K11" s="57"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A12" s="53"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="51"/>
+      <c r="A12" s="73"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="67"/>
       <c r="J12" s="56"/>
       <c r="K12" s="57"/>
     </row>
     <row r="13" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="51"/>
+      <c r="A13" s="73"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="67"/>
       <c r="J13" s="56"/>
       <c r="K13" s="57"/>
     </row>
     <row r="14" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A14" s="53"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="51"/>
+      <c r="A14" s="73"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="67"/>
       <c r="J14" s="56"/>
       <c r="K14" s="57"/>
     </row>
     <row r="15" spans="1:11" ht="12" customHeight="1">
-      <c r="A15" s="53"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="51"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="67"/>
       <c r="J15" s="56"/>
       <c r="K15" s="57"/>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
-      <c r="A16" s="53"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="51"/>
+      <c r="A16" s="73"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="67"/>
       <c r="J16" s="56"/>
       <c r="K16" s="57"/>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1">
-      <c r="A17" s="53"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
+      <c r="A17" s="73"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
       <c r="J17" s="48"/>
       <c r="K17" s="48"/>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
-      <c r="A18" s="53"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="51" t="s">
+      <c r="A18" s="73"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="67" t="s">
         <v>6</v>
       </c>
       <c r="J18" s="54" t="s">
@@ -4179,66 +4539,66 @@
       <c r="K18" s="55"/>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
-      <c r="A19" s="53"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="51"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="67"/>
       <c r="J19" s="56"/>
       <c r="K19" s="57"/>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1">
-      <c r="A20" s="53"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="51"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="67"/>
       <c r="J20" s="56"/>
       <c r="K20" s="57"/>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
-      <c r="A21" s="53"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="51"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="67"/>
       <c r="J21" s="56"/>
       <c r="K21" s="57"/>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1">
-      <c r="A22" s="53"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="67"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
       <c r="J22" s="48"/>
       <c r="K22" s="48"/>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="51" t="s">
+      <c r="A23" s="73"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="67" t="s">
         <v>6</v>
       </c>
       <c r="J23" s="63" t="s">
@@ -4247,41 +4607,41 @@
       <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
-      <c r="A24" s="53"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="51"/>
+      <c r="A24" s="73"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="67"/>
       <c r="J24" s="65"/>
       <c r="K24" s="66"/>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
-      <c r="A25" s="53"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="51"/>
+      <c r="A25" s="73"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="67"/>
       <c r="J25" s="65"/>
       <c r="K25" s="66"/>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
-      <c r="A26" s="53"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="51"/>
+      <c r="A26" s="73"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="67"/>
       <c r="J26" s="65"/>
       <c r="K26" s="66"/>
     </row>
@@ -4294,12 +4654,12 @@
     </row>
     <row r="30" spans="1:11" ht="20.25" customHeight="1">
       <c r="A30" s="3"/>
-      <c r="B30" s="49" t="s">
+      <c r="B30" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="95"/>
       <c r="G30" s="60" t="s">
         <v>14</v>
       </c>
@@ -4314,12 +4674,12 @@
     </row>
     <row r="31" spans="1:11" ht="20.25" customHeight="1">
       <c r="A31" s="5"/>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="95"/>
+      <c r="E31" s="95"/>
       <c r="G31" s="58" t="s">
         <v>7</v>
       </c>
@@ -4334,12 +4694,12 @@
     </row>
     <row r="32" spans="1:11" ht="20.25" customHeight="1">
       <c r="A32" s="7"/>
-      <c r="B32" s="49" t="s">
+      <c r="B32" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="95"/>
       <c r="G32" s="58" t="s">
         <v>8</v>
       </c>
@@ -4354,21 +4714,21 @@
     </row>
     <row r="33" spans="1:5" ht="20.25" customHeight="1">
       <c r="A33" s="8"/>
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="95"/>
     </row>
     <row r="34" spans="1:5" ht="19.5" customHeight="1">
       <c r="A34" s="9"/>
-      <c r="B34" s="49" t="s">
+      <c r="B34" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="95"/>
     </row>
     <row r="37" spans="1:5"/>
     <row r="38" spans="1:5"/>
@@ -4376,11 +4736,16 @@
     <row r="40" spans="1:5"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="F5:F26"/>
+    <mergeCell ref="C5:C26"/>
+    <mergeCell ref="I5:I16"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="A5:B26"/>
+    <mergeCell ref="D5:E26"/>
     <mergeCell ref="J5:K16"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="I32:J32"/>
@@ -4393,16 +4758,11 @@
     <mergeCell ref="I18:I21"/>
     <mergeCell ref="I23:I26"/>
     <mergeCell ref="G5:H26"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="F5:F26"/>
-    <mergeCell ref="C5:C26"/>
-    <mergeCell ref="I5:I16"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="A5:B26"/>
-    <mergeCell ref="D5:E26"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4411,7 +4771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD946C15-825B-4BE7-A8B4-0C1FA4B1BA8B}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -4420,7 +4780,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1">
+    <row r="1" spans="1:6" ht="15.75" thickBot="1">
       <c r="A1" s="11" t="s">
         <v>22</v>
       </c>
@@ -4434,7 +4794,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="21" customHeight="1">
+    <row r="2" spans="1:6" ht="21" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -4445,7 +4805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -4459,18 +4819,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="409.6">
+    <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="95" t="s">
+      <c r="C4" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
@@ -4480,6 +4840,19 @@
       <c r="C5" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="F5"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4501,7 +4874,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="48.75" customHeight="1">
       <c r="A1" s="74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
@@ -4510,19 +4883,19 @@
     </row>
     <row r="2" spans="1:5" ht="18.75" customHeight="1">
       <c r="A2" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="48.75" customHeight="1">
@@ -4533,13 +4906,13 @@
         <v>8</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18.75" customHeight="1">
@@ -4551,7 +4924,7 @@
     </row>
     <row r="5" spans="1:5" ht="23.25" customHeight="1">
       <c r="A5" s="76" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="77"/>
       <c r="C5" s="77"/>
@@ -4563,492 +4936,492 @@
         <v>23</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="48.75" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48.75" customHeight="1">
       <c r="A8" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="48.75" customHeight="1">
       <c r="A9" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="48.75" customHeight="1">
       <c r="A10" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="48.75" customHeight="1">
       <c r="A11" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="48.75" customHeight="1">
       <c r="A12" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E12" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="48.75" customHeight="1">
       <c r="A13" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="48.75" customHeight="1">
       <c r="A14" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="48.75" customHeight="1">
       <c r="A15" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="32" customFormat="1" ht="48.75" customHeight="1">
       <c r="A16" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="48.75" customHeight="1">
       <c r="A17" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="48.75" customHeight="1">
       <c r="A18" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="48.75" customHeight="1">
       <c r="A19" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="48.75" customHeight="1">
       <c r="A20" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="48.75" customHeight="1">
       <c r="A21" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D21" s="30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="48.75" customHeight="1">
       <c r="A22" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D22" s="30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="48.75" customHeight="1">
       <c r="A23" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" s="30" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="48.75" customHeight="1">
       <c r="A24" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="48.75" customHeight="1">
       <c r="A25" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B25" s="30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E25" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="48.75" customHeight="1">
       <c r="A26" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E26" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="48.75" customHeight="1">
       <c r="A27" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E27" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="48.75" customHeight="1">
       <c r="A28" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E28" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="48.75" customHeight="1">
       <c r="A29" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29" s="30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E29" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="48.75" customHeight="1">
       <c r="A30" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E30" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="48.75" customHeight="1">
       <c r="A31" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E31" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="48.75" customHeight="1">
       <c r="A32" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E32" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="48.75" customHeight="1">
       <c r="A33" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E33" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="48.75" customHeight="1">
       <c r="A34" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E34" s="30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="48.75" customHeight="1">
@@ -5082,64 +5455,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="51" customHeight="1">
-      <c r="A1" s="87" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
+      <c r="A1" s="80" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="90"/>
+      <c r="B2" s="82" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="83"/>
       <c r="D2" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="222" customHeight="1">
       <c r="A3" s="15">
         <v>1</v>
       </c>
-      <c r="B3" s="91" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="92"/>
+      <c r="B3" s="84" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="85"/>
       <c r="D3" s="16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="153.75" customHeight="1">
       <c r="A4" s="41">
         <v>2</v>
       </c>
-      <c r="B4" s="83" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="83"/>
+      <c r="B4" s="86" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="86"/>
       <c r="D4" s="42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" s="43"/>
     </row>
@@ -5147,15 +5520,15 @@
       <c r="A5" s="41">
         <v>3</v>
       </c>
-      <c r="B5" s="93" t="s">
+      <c r="B5" s="87" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="88"/>
+      <c r="D5" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="43" t="s">
         <v>113</v>
-      </c>
-      <c r="C5" s="94"/>
-      <c r="D5" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>112</v>
       </c>
       <c r="F5" s="43"/>
     </row>
@@ -5163,33 +5536,33 @@
       <c r="A6" s="41">
         <v>4</v>
       </c>
-      <c r="B6" s="85" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="85"/>
+      <c r="B6" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="79"/>
       <c r="D6" s="42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="113.25" customHeight="1">
       <c r="A7" s="41">
         <v>5</v>
       </c>
-      <c r="B7" s="85" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="85"/>
+      <c r="B7" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="79"/>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F7" s="43"/>
     </row>
@@ -5197,15 +5570,15 @@
       <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="86" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="86"/>
+      <c r="B8" s="90" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="90"/>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F8" s="43"/>
     </row>
@@ -5213,15 +5586,15 @@
       <c r="A9" s="41">
         <v>7</v>
       </c>
-      <c r="B9" s="83" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="83"/>
+      <c r="B9" s="86" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="86"/>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" s="43"/>
     </row>
@@ -5229,263 +5602,263 @@
       <c r="A10" s="41">
         <v>8</v>
       </c>
-      <c r="B10" s="79" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="79"/>
+      <c r="B10" s="89" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="89"/>
       <c r="D10" s="45"/>
       <c r="E10" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="408.75" customHeight="1">
       <c r="A11" s="41">
         <v>9</v>
       </c>
-      <c r="B11" s="79" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="79"/>
+      <c r="B11" s="89" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="89"/>
       <c r="D11"/>
       <c r="E11" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="105" customHeight="1">
       <c r="A12" s="41">
         <v>10</v>
       </c>
-      <c r="B12" s="83" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="83"/>
+      <c r="B12" s="86" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="86"/>
       <c r="D12"/>
       <c r="E12" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F12" s="43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="156.75" customHeight="1">
       <c r="A13" s="41">
         <v>11</v>
       </c>
-      <c r="B13" s="83" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="83"/>
+      <c r="B13" s="86" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="86"/>
       <c r="D13"/>
       <c r="E13" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="118.5" customHeight="1">
       <c r="A14" s="41">
         <v>12</v>
       </c>
-      <c r="B14" s="79" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" s="79"/>
+      <c r="B14" s="89" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="89"/>
       <c r="D14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F14" s="43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="275.25" customHeight="1">
       <c r="A15" s="41">
         <v>13</v>
       </c>
-      <c r="B15" s="79" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="79"/>
+      <c r="B15" s="89" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="89"/>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F15" s="43" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="309" customHeight="1">
       <c r="A16" s="41">
         <v>14</v>
       </c>
-      <c r="B16" s="79" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="79"/>
+      <c r="B16" s="89" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="89"/>
       <c r="D16"/>
       <c r="E16" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F16" s="43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="351.75" customHeight="1">
       <c r="A17" s="41">
         <v>15</v>
       </c>
-      <c r="B17" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="79"/>
+      <c r="B17" s="89" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="89"/>
       <c r="D17"/>
       <c r="E17" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F17" s="43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="202.5" customHeight="1">
       <c r="A18" s="41">
         <v>16</v>
       </c>
-      <c r="B18" s="79" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="79"/>
+      <c r="B18" s="89" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="89"/>
       <c r="D18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E18" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F18" s="43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="327" customHeight="1">
       <c r="A19" s="41">
         <v>17</v>
       </c>
-      <c r="B19" s="79" t="s">
-        <v>146</v>
-      </c>
-      <c r="C19" s="79"/>
+      <c r="B19" s="89" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="89"/>
       <c r="D19"/>
       <c r="E19" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="324" customHeight="1">
       <c r="A20" s="41">
         <v>18</v>
       </c>
-      <c r="B20" s="79" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="79"/>
+      <c r="B20" s="89" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" s="89"/>
       <c r="D20"/>
       <c r="E20" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F20" s="43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="275.25" customHeight="1">
       <c r="A21" s="41">
         <v>19</v>
       </c>
-      <c r="B21" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="79"/>
+      <c r="B21" s="89" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" s="89"/>
       <c r="D21" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E21" s="43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F21" s="43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="381.75" customHeight="1">
       <c r="A22" s="46">
         <v>20</v>
       </c>
-      <c r="B22" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="79"/>
+      <c r="B22" s="89" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="89"/>
       <c r="D22" s="18"/>
       <c r="E22" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F22" s="43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="381.75" customHeight="1">
       <c r="A23" s="46">
         <v>21</v>
       </c>
-      <c r="B23" s="79" t="s">
-        <v>155</v>
-      </c>
-      <c r="C23" s="79"/>
+      <c r="B23" s="89" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="89"/>
       <c r="D23" s="18"/>
       <c r="E23" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F23" s="43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="134.25" customHeight="1">
       <c r="A24" s="46">
         <v>22</v>
       </c>
-      <c r="B24" s="83" t="s">
-        <v>157</v>
-      </c>
-      <c r="C24" s="83"/>
+      <c r="B24" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="86"/>
       <c r="D24" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E24" s="43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F24" s="43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="408" customHeight="1">
       <c r="A25" s="46">
         <v>23</v>
       </c>
-      <c r="B25" s="79" t="s">
-        <v>161</v>
-      </c>
-      <c r="C25" s="79"/>
+      <c r="B25" s="89" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="89"/>
       <c r="D25" s="18"/>
       <c r="E25" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F25" s="43"/>
     </row>
@@ -5493,13 +5866,13 @@
       <c r="A26" s="46">
         <v>24</v>
       </c>
-      <c r="B26" s="79" t="s">
-        <v>162</v>
-      </c>
-      <c r="C26" s="79"/>
+      <c r="B26" s="89" t="s">
+        <v>163</v>
+      </c>
+      <c r="C26" s="89"/>
       <c r="D26" s="18"/>
       <c r="E26" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F26" s="43"/>
     </row>
@@ -5507,186 +5880,186 @@
       <c r="A27" s="46">
         <v>25</v>
       </c>
-      <c r="B27" s="84" t="s">
-        <v>163</v>
-      </c>
-      <c r="C27" s="84"/>
+      <c r="B27" s="91" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="91"/>
       <c r="D27" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E27" s="43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F27" s="43" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="240" customHeight="1">
       <c r="A28" s="46">
         <v>26</v>
       </c>
-      <c r="B28" s="79" t="s">
-        <v>166</v>
-      </c>
-      <c r="C28" s="79"/>
+      <c r="B28" s="89" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="89"/>
       <c r="D28" s="18"/>
       <c r="E28" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="213" customHeight="1">
       <c r="A29" s="46">
         <v>27</v>
       </c>
-      <c r="B29" s="79" t="s">
-        <v>168</v>
-      </c>
-      <c r="C29" s="79"/>
+      <c r="B29" s="89" t="s">
+        <v>169</v>
+      </c>
+      <c r="C29" s="89"/>
       <c r="D29" s="18"/>
       <c r="E29" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="170.25" customHeight="1">
       <c r="A30" s="46">
         <v>28</v>
       </c>
-      <c r="B30" s="83" t="s">
-        <v>170</v>
-      </c>
-      <c r="C30" s="83"/>
+      <c r="B30" s="86" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" s="86"/>
       <c r="D30" s="18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E30" s="43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F30" s="43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="229.5" customHeight="1">
       <c r="A31" s="46">
         <v>29</v>
       </c>
-      <c r="B31" s="79" t="s">
-        <v>173</v>
-      </c>
-      <c r="C31" s="79"/>
+      <c r="B31" s="89" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="89"/>
       <c r="D31" s="18"/>
       <c r="E31" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F31" s="43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="170.25" customHeight="1">
       <c r="A32" s="46">
         <v>30</v>
       </c>
-      <c r="B32" s="79" t="s">
-        <v>175</v>
-      </c>
-      <c r="C32" s="79"/>
+      <c r="B32" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="C32" s="89"/>
       <c r="D32" s="18"/>
       <c r="E32" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="182.25" customHeight="1">
       <c r="A33" s="46">
         <v>31</v>
       </c>
-      <c r="B33" s="79" t="s">
-        <v>177</v>
-      </c>
-      <c r="C33" s="79"/>
+      <c r="B33" s="89" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="89"/>
       <c r="D33" s="18"/>
       <c r="E33" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F33" s="43" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="186" customHeight="1">
       <c r="A34" s="46">
         <v>32</v>
       </c>
-      <c r="B34" s="83" t="s">
-        <v>179</v>
-      </c>
-      <c r="C34" s="83"/>
+      <c r="B34" s="86" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" s="86"/>
       <c r="D34" s="18"/>
       <c r="E34" s="43" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="186" customHeight="1">
       <c r="A35" s="46">
         <v>33</v>
       </c>
-      <c r="B35" s="79" t="s">
-        <v>181</v>
-      </c>
-      <c r="C35" s="79"/>
+      <c r="B35" s="89" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" s="89"/>
       <c r="D35" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E35" s="43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F35" s="43" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="186" customHeight="1">
       <c r="A36" s="46">
         <v>34</v>
       </c>
-      <c r="B36" s="79" t="s">
-        <v>184</v>
-      </c>
-      <c r="C36" s="79"/>
+      <c r="B36" s="89" t="s">
+        <v>185</v>
+      </c>
+      <c r="C36" s="89"/>
       <c r="D36" s="18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E36" s="43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F36" s="43" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="186" customHeight="1">
       <c r="A37" s="46">
         <v>35</v>
       </c>
-      <c r="B37" s="79" t="s">
-        <v>187</v>
-      </c>
-      <c r="C37" s="79"/>
+      <c r="B37" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="C37" s="89"/>
       <c r="D37" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E37" s="43" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F37" s="43" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -5699,7 +6072,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B39" s="34"/>
       <c r="C39" s="34"/>
@@ -5708,33 +6081,33 @@
       <c r="F39" s="34"/>
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A40" s="80" t="s">
-        <v>191</v>
-      </c>
-      <c r="B40" s="81"/>
-      <c r="C40" s="81"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="81"/>
-      <c r="F40" s="82"/>
+      <c r="A40" s="92" t="s">
+        <v>192</v>
+      </c>
+      <c r="B40" s="93"/>
+      <c r="C40" s="93"/>
+      <c r="D40" s="93"/>
+      <c r="E40" s="93"/>
+      <c r="F40" s="94"/>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1">
       <c r="A41" s="36" t="s">
         <v>23</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="42.75" customHeight="1">
@@ -5742,19 +6115,19 @@
         <v>8</v>
       </c>
       <c r="B42" s="39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D42" s="40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="27" customHeight="1">
@@ -5762,19 +6135,19 @@
         <v>8</v>
       </c>
       <c r="B43" s="39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" s="39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D43" s="40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E43" s="39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F43" s="39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="24" customHeight="1">
@@ -5782,19 +6155,19 @@
         <v>8</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D44" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="38.25" customHeight="1">
@@ -5802,19 +6175,19 @@
         <v>8</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C45" s="39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="1:6" s="47" customFormat="1" ht="124.5" customHeight="1">
@@ -5822,19 +6195,19 @@
         <v>8</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C46" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D46" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="23.25" customHeight="1">
@@ -5842,19 +6215,19 @@
         <v>8</v>
       </c>
       <c r="B47" s="39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C47" s="39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D47" s="39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E47" s="39" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F47" s="39" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -5862,19 +6235,19 @@
         <v>8</v>
       </c>
       <c r="B48" s="39" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C48" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -5882,19 +6255,19 @@
         <v>8</v>
       </c>
       <c r="B49" s="39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C49" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D49" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E49" s="39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F49" s="39" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -5902,19 +6275,19 @@
         <v>8</v>
       </c>
       <c r="B50" s="39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F50" s="39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -5922,19 +6295,19 @@
         <v>8</v>
       </c>
       <c r="B51" s="39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C51" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E51" s="39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F51" s="39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -5942,19 +6315,19 @@
         <v>8</v>
       </c>
       <c r="B52" s="39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C52" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D52" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E52" s="39" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F52" s="39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -5962,19 +6335,19 @@
         <v>8</v>
       </c>
       <c r="B53" s="39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" s="39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D53" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E53" s="39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F53" s="39" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -5982,19 +6355,19 @@
         <v>8</v>
       </c>
       <c r="B54" s="39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C54" s="39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D54" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E54" s="39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F54" s="39" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -6002,19 +6375,19 @@
         <v>8</v>
       </c>
       <c r="B55" s="39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" s="39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D55" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E55" s="39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F55" s="39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -6022,19 +6395,19 @@
         <v>8</v>
       </c>
       <c r="B56" s="39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D56" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -6042,19 +6415,19 @@
         <v>8</v>
       </c>
       <c r="B57" s="39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C57" s="39" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D57" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E57" s="39" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F57" s="39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -6062,19 +6435,19 @@
         <v>8</v>
       </c>
       <c r="B58" s="39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C58" s="39" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D58" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E58" s="39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="95.25" customHeight="1">
@@ -6082,19 +6455,19 @@
         <v>8</v>
       </c>
       <c r="B59" s="39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C59" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D59" s="40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E59" s="39" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F59" s="39" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -6102,16 +6475,16 @@
         <v>8</v>
       </c>
       <c r="B60" s="39" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C60" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D60" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E60" s="39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F60" s="39"/>
     </row>
@@ -6120,19 +6493,19 @@
         <v>8</v>
       </c>
       <c r="B61" s="39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C61" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D61" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E61" s="39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F61" s="39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="108" customHeight="1">
@@ -6140,19 +6513,19 @@
         <v>8</v>
       </c>
       <c r="B62" s="39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C62" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D62" s="40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E62" s="39" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F62" s="39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="105" customHeight="1">
@@ -6160,19 +6533,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C63" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D63" s="40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E63" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="F63" s="39" t="s">
         <v>230</v>
-      </c>
-      <c r="F63" s="39" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="111" customHeight="1">
@@ -6180,19 +6553,19 @@
         <v>8</v>
       </c>
       <c r="B64" s="39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C64" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D64" s="40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E64" s="39" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F64" s="39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="99.75" customHeight="1">
@@ -6200,19 +6573,19 @@
         <v>8</v>
       </c>
       <c r="B65" s="39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C65" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E65" s="39" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F65" s="39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="103.5" customHeight="1">
@@ -6220,19 +6593,19 @@
         <v>8</v>
       </c>
       <c r="B66" s="39" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C66" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D66" s="40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E66" s="39" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F66" s="39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="106.5" customHeight="1">
@@ -6240,19 +6613,19 @@
         <v>8</v>
       </c>
       <c r="B67" s="39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C67" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D67" s="40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E67" s="39" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F67" s="39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="109.5" customHeight="1">
@@ -6260,19 +6633,19 @@
         <v>8</v>
       </c>
       <c r="B68" s="39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C68" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D68" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E68" s="39" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F68" s="39" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -6280,19 +6653,19 @@
         <v>8</v>
       </c>
       <c r="B69" s="39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C69" s="39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D69" s="39" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E69" s="39" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F69" s="39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -6300,19 +6673,19 @@
         <v>8</v>
       </c>
       <c r="B70" s="39" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C70" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D70" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E70" s="39" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F70" s="39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -6320,19 +6693,19 @@
         <v>8</v>
       </c>
       <c r="B71" s="39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C71" s="39" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E71" s="39" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F71" s="39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -6340,27 +6713,41 @@
         <v>8</v>
       </c>
       <c r="B72" s="39" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C72" s="39" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D72" s="39" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E72" s="39"/>
       <c r="F72" s="39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -6373,26 +6760,12 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6571,15 +6944,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -6589,14 +6953,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF69206-D903-4973-BD90-FEDD12C88DA5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B956392-AAE6-4DA6-9CA7-D8DB636C01A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B079ADB8-D386-4C38-9FD3-437EE2FC6D11}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B079ADB8-D386-4C38-9FD3-437EE2FC6D11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B956392-AAE6-4DA6-9CA7-D8DB636C01A2}"/>
 </file>
--- a/input/mapping/009. OCB_GOLD_TCKH_V_CUST_STATUS_NEW_BAOANH.xlsx
+++ b/input/mapping/009. OCB_GOLD_TCKH_V_CUST_STATUS_NEW_BAOANH.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/ANHPB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1807" documentId="13_ncr:1_{65A8DFCB-4547-420A-82EC-B4C57912D235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9558EFCE-4D33-4DA4-B2AF-D06EBBAF504F}"/>
+  <xr:revisionPtr revIDLastSave="1842" documentId="13_ncr:1_{65A8DFCB-4547-420A-82EC-B4C57912D235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FE4E1CA-B4E3-4928-828B-23B3A9527BDD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{D1E0AC4A-EE92-4A85-8B4C-1D02E566321C}"/>
   </bookViews>
@@ -250,42 +250,8 @@
 </t>
   </si>
   <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CST_LCS_KT_30D_FINAL_CASE5 (
-    DATA_DT                 DATE,
-    CIF                     DECIMAL(10,0),
-    T_COMPANY_BOOK          STRING,
-    T_CREATE_DATE           DATE NOT NULL,
-    FINAL_STATUS            STRING,
-    SCTR                    DECIMAL(10,0),
-    T_DESCRIPTION           STRING,
-    CST_GRP                 STRING,
-    CUST_GROUP_NAME         STRING,
-    CUST_GROUP_LINE         STRING,
-    CUST_GROUP_LINE_SHORT   STRING,
-    TIENGUI                 DECIMAL(20,4),
-    TIENVAY                 DECIMAL(20,4),
-    CUST_CURRENT_ACCT_A1    DECIMAL(20,4),
-    CIF_LOANCLASS            DECIMAL(3,0),
-    DOANHSO_BAOLANH_30D     DECIMAL(31,4),
-    DOANHSO_LC_30D          DECIMAL(31,4),
-    NUM_TRANS               INT,
-    ACTIVE_INDEX            INT,
-    T24_STATUS              STRING,
-    T24_ACTIVE_RB           INT,
-    T24_ACTIVE_COMB         INT,
-    T24_ACTIVE_TRE          INT,
-    T24_ACTIVE_CIB          INT,
-    T24_ACTIVE_CMB          INT,
-    T24_ACTIVE_DCTC         INT,
-    T24_ACTIVE_LIO          INT,
-    W4_STATUS               STRING,
-    W4_ACTIVE_RB            INT,
-    W4_ACTIVE_LIO           INT,
-    DATE_SYS                TIMESTAMP
-)
-USING DELTA;
 INSERT INTO CST_LCS_KT_30D_FINAL_CASE5
 REPLACE WHERE DATA_DT = to_date(:DATADT, 'yyyyMMdd')
 WITH
@@ -426,7 +392,7 @@
 cte_cust_group AS (
     SELECT
         ocg.ref_code,
-        max_by(ocg.ref_description, ocg.source_event_date) AS cust_group_name   -- cột 9
+        max_by(ocg.ref_description, ocg.source_event_date) AS cust_group_name  
     FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_ocbh_cus_group') ocg
     WHERE ocg.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ocg.ref_code
@@ -447,7 +413,7 @@
         max_by(ccb.so_du_bao_lanh, ccb.source_event_date) AS so_du_bao_lanh,
         max_by(ccb.so_du_lc,       ccb.source_event_date) AS so_du_lc
     FROM IDENTIFIER(:cleaned || '.business_vault.csat_customer_sum_balance') ccb
-    WHERE ccb.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
+    WHERE ccb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
     GROUP BY ccb.customer_hashkey
 ),
 cte_acct_base AS (   -- Bước 1
@@ -569,7 +535,7 @@
     LEFT JOIN cte_md_deal_sts_del d_md
       ON d_md.md_deal_hashkey = smdi.md_deal_hashkey
     WHERE smdi.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
-      AND smdi.t_value_date BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
+      AND to_date(smdi.t_value_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
       AND d_md.md_deal_hashkey IS NULL
     GROUP BY smdi.md_deal_hashkey
 ),
@@ -584,10 +550,13 @@
       ON hmd.md_deal_hashkey = md1.md_deal_hashkey
     JOIN cte_snap_hub_crb hcb
       ON hcb.tieukhoan = hmd.business_key AND hcb.gl &lt;&gt; '9995'
+    LEFT JOIN cte_crb_sts_del d_crb                                   
+      ON d_crb.crb_hashkey = hcb.crb_hashkey                         
     LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_crb_balance') scb
-      ON scb.crb_hashkey = hcb.crb_hashkey
-     AND scb.ma_key BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
-     AND scb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    ON scb.crb_hashkey = hcb.crb_hashkey
+    AND to_date(scb.ma_key, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
+    AND scb.source_event_date = to_date(:DATADT, 'yyyyMMdd')
+    WHERE d_crb.crb_hashkey IS NULL                                 
 ),
 cte_doanhso_baolanh_30d AS (  
     SELECT
@@ -604,7 +573,7 @@
         max_by(slct.t_issue_date, slct.source_event_date) AS t_issue_date
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_letter_of_credit_terms') slct
     WHERE slct.source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
-      AND slct.t_issue_date BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
+    AND to_date(slct.t_issue_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
     GROUP BY slct.letter_of_credit_hashkey
 ),
 cte_lc_value AS (  
@@ -655,7 +624,7 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_currency') rc
       ON rc.id = v.t_lc_currency
      AND v.issue_date = rc.data_date
-     AND rc.data_date BETWEEN date_format(DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30), 'yyyyMMdd') AND :DATADT
+     AND to_date(rc.data_date, 'yyyyMMdd') BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -30) AND to_date(:DATADT, 'yyyyMMdd')
     JOIN cte_lc_customer cust
       ON cust.letter_of_credit_hashkey = v.letter_of_credit_hashkey
     GROUP BY cust.customer_hashkey
@@ -822,10 +791,10 @@
       ON c.customer_hashkey = s.customer_hashkey
 ),
 cte_prev_bsn_day AS (   
-    SELECT MAX(msr_prd_id) AS prev_bsn_day
+    SELECT MAX(to_date(msr_prd_id, 'yyyyMMdd')) AS prev_bsn_day
     FROM cte_snap_calendar
     WHERE bsn_day_f = 1
-      AND msr_prd_id &lt; to_date(:DATADT, 'yyyyMMdd')
+      AND to_date(msr_prd_id, 'yyyyMMdd') &lt; to_date(:DATADT, 'yyyyMMdd')
 ),
 cte_new_cust AS (  
     SELECT bc.customer_hashkey
@@ -918,10 +887,8 @@
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_acnt_contract_information')
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY acnt_contract_hashkey
-),</t>
-  </si>
-  <si>
-    <t>cte_w4_acnt_contract_type_cur AS (   
+),
+cte_w4_acnt_contract_type_cur AS (   
     SELECT
         acnt_contract_hashkey,
         max_by(con_cat,  source_event_date) AS con_cat,
@@ -930,7 +897,10 @@
     WHERE source_event_date &lt;= to_date(:DATADT, 'yyyyMMdd')
     GROUP BY acnt_contract_hashkey
 ),
-cte_w4_acnt_contract_branch_cur AS (
+</t>
+  </si>
+  <si>
+    <t>cte_w4_acnt_contract_branch_cur AS (
     SELECT
         acnt_contract_hashkey,
         max_by(branch_hashkey, source_event_date) AS branch_hashkey
@@ -1123,8 +1093,8 @@
                        BETWEEN DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180) AND DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -31)
                  THEN 1 ELSE 0 END AS trans_31_120d,
             CASE WHEN to_date(base.last_trans_date, 'yyyyMMdd') &lt; DATE_ADD(to_date(:DATADT, 'yyyyMMdd'), -180)
-                  AND base.last_trans_date &gt; '19000101'
-                 THEN 1 ELSE 0 END AS trans_121d
+                AND to_date(base.last_trans_date, 'yyyyMMdd') &gt; to_date('19000101', 'yyyyMMdd')
+                THEN 1 ELSE 0 END AS trans_121d
         FROM cte_w4_card_contract base
         LEFT JOIN cte_w4_balance bl ON bl.issuing_hashkey = base.issuing_hashkey
         LEFT JOIN cte_w4_loan_class lcls ON lcls.so_hd = base.issuing_number
@@ -3776,6 +3746,66 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3791,66 +3821,6 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3866,9 +3836,30 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3887,31 +3878,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -4302,63 +4272,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="42" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
     </row>
     <row r="2" spans="1:11" ht="8.25" customHeight="1"/>
     <row r="3" spans="1:11" ht="26.25" customHeight="1">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="D3" s="53" t="s">
+      <c r="B3" s="70"/>
+      <c r="D3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="50"/>
+      <c r="E3" s="70"/>
       <c r="F3" s="10"/>
-      <c r="G3" s="49" t="s">
+      <c r="G3" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="50"/>
-      <c r="J3" s="49" t="s">
+      <c r="H3" s="70"/>
+      <c r="J3" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="50"/>
+      <c r="K3" s="70"/>
     </row>
     <row r="4" spans="1:11" ht="8.25" customHeight="1">
       <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="67" t="s">
+      <c r="B5" s="52"/>
+      <c r="C5" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="71" t="s">
+      <c r="E5" s="52"/>
+      <c r="F5" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="G5" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="67" t="s">
+      <c r="H5" s="67"/>
+      <c r="I5" s="51" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="54" t="s">
@@ -4367,170 +4337,170 @@
       <c r="K5" s="55"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1">
-      <c r="A6" s="73"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="67"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="51"/>
       <c r="J6" s="56"/>
       <c r="K6" s="57"/>
     </row>
     <row r="7" spans="1:11" ht="12" customHeight="1">
-      <c r="A7" s="73"/>
-      <c r="B7" s="73"/>
-      <c r="C7" s="67"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
-      <c r="I7" s="67"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="51"/>
       <c r="J7" s="56"/>
       <c r="K7" s="57"/>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1">
-      <c r="A8" s="73"/>
-      <c r="B8" s="73"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="67"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="51"/>
       <c r="J8" s="56"/>
       <c r="K8" s="57"/>
     </row>
     <row r="9" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A9" s="73"/>
-      <c r="B9" s="73"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="69"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="67"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="51"/>
       <c r="J9" s="56"/>
       <c r="K9" s="57"/>
     </row>
     <row r="10" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A10" s="73"/>
-      <c r="B10" s="73"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="67"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="50"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="51"/>
       <c r="J10" s="56"/>
       <c r="K10" s="57"/>
     </row>
     <row r="11" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="69"/>
-      <c r="H11" s="69"/>
-      <c r="I11" s="67"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="51"/>
       <c r="J11" s="56"/>
       <c r="K11" s="57"/>
     </row>
     <row r="12" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A12" s="73"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="71"/>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="67"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="51"/>
       <c r="J12" s="56"/>
       <c r="K12" s="57"/>
     </row>
     <row r="13" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A13" s="73"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="67"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+      <c r="I13" s="51"/>
       <c r="J13" s="56"/>
       <c r="K13" s="57"/>
     </row>
     <row r="14" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A14" s="73"/>
-      <c r="B14" s="73"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="71"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="67"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="51"/>
       <c r="J14" s="56"/>
       <c r="K14" s="57"/>
     </row>
     <row r="15" spans="1:11" ht="12" customHeight="1">
-      <c r="A15" s="73"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="67"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="51"/>
       <c r="J15" s="56"/>
       <c r="K15" s="57"/>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1">
-      <c r="A16" s="73"/>
-      <c r="B16" s="73"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="69"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="67"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="68"/>
+      <c r="I16" s="51"/>
       <c r="J16" s="56"/>
       <c r="K16" s="57"/>
     </row>
     <row r="17" spans="1:11" ht="30" customHeight="1">
-      <c r="A17" s="73"/>
-      <c r="B17" s="73"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
       <c r="J17" s="48"/>
       <c r="K17" s="48"/>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1">
-      <c r="A18" s="73"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="71"/>
-      <c r="G18" s="69"/>
-      <c r="H18" s="69"/>
-      <c r="I18" s="67" t="s">
+      <c r="A18" s="53"/>
+      <c r="B18" s="53"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="51" t="s">
         <v>6</v>
       </c>
       <c r="J18" s="54" t="s">
@@ -4539,66 +4509,66 @@
       <c r="K18" s="55"/>
     </row>
     <row r="19" spans="1:11" ht="30" customHeight="1">
-      <c r="A19" s="73"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="67"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="51"/>
       <c r="J19" s="56"/>
       <c r="K19" s="57"/>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1">
-      <c r="A20" s="73"/>
-      <c r="B20" s="73"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="71"/>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
-      <c r="I20" s="67"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="51"/>
       <c r="J20" s="56"/>
       <c r="K20" s="57"/>
     </row>
     <row r="21" spans="1:11" ht="30" customHeight="1">
-      <c r="A21" s="73"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="69"/>
-      <c r="H21" s="69"/>
-      <c r="I21" s="67"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="51"/>
       <c r="J21" s="56"/>
       <c r="K21" s="57"/>
     </row>
     <row r="22" spans="1:11" ht="30" customHeight="1">
-      <c r="A22" s="73"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
       <c r="J22" s="48"/>
       <c r="K22" s="48"/>
     </row>
     <row r="23" spans="1:11" ht="30" customHeight="1">
-      <c r="A23" s="73"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="67" t="s">
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="51" t="s">
         <v>6</v>
       </c>
       <c r="J23" s="63" t="s">
@@ -4607,41 +4577,41 @@
       <c r="K23" s="64"/>
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
-      <c r="A24" s="73"/>
-      <c r="B24" s="73"/>
-      <c r="C24" s="67"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="69"/>
-      <c r="H24" s="69"/>
-      <c r="I24" s="67"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="51"/>
       <c r="J24" s="65"/>
       <c r="K24" s="66"/>
     </row>
     <row r="25" spans="1:11" ht="30" customHeight="1">
-      <c r="A25" s="73"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
-      <c r="I25" s="67"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
+      <c r="I25" s="51"/>
       <c r="J25" s="65"/>
       <c r="K25" s="66"/>
     </row>
     <row r="26" spans="1:11" ht="30" customHeight="1">
-      <c r="A26" s="73"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
-      <c r="I26" s="67"/>
+      <c r="A26" s="53"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="51"/>
       <c r="J26" s="65"/>
       <c r="K26" s="66"/>
     </row>
@@ -4654,7 +4624,7 @@
     </row>
     <row r="30" spans="1:11" ht="20.25" customHeight="1">
       <c r="A30" s="3"/>
-      <c r="B30" s="70" t="s">
+      <c r="B30" s="49" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="95"/>
@@ -4674,7 +4644,7 @@
     </row>
     <row r="31" spans="1:11" ht="20.25" customHeight="1">
       <c r="A31" s="5"/>
-      <c r="B31" s="70" t="s">
+      <c r="B31" s="49" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="95"/>
@@ -4694,7 +4664,7 @@
     </row>
     <row r="32" spans="1:11" ht="20.25" customHeight="1">
       <c r="A32" s="7"/>
-      <c r="B32" s="70" t="s">
+      <c r="B32" s="49" t="s">
         <v>19</v>
       </c>
       <c r="C32" s="95"/>
@@ -4714,7 +4684,7 @@
     </row>
     <row r="33" spans="1:5" ht="20.25" customHeight="1">
       <c r="A33" s="8"/>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="49" t="s">
         <v>20</v>
       </c>
       <c r="C33" s="95"/>
@@ -4723,7 +4693,7 @@
     </row>
     <row r="34" spans="1:5" ht="19.5" customHeight="1">
       <c r="A34" s="9"/>
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="49" t="s">
         <v>21</v>
       </c>
       <c r="C34" s="95"/>
@@ -4736,16 +4706,11 @@
     <row r="40" spans="1:5"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="F5:F26"/>
-    <mergeCell ref="C5:C26"/>
-    <mergeCell ref="I5:I16"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="A5:B26"/>
-    <mergeCell ref="D5:E26"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:H3"/>
     <mergeCell ref="J5:K16"/>
     <mergeCell ref="G32:H32"/>
     <mergeCell ref="I32:J32"/>
@@ -4758,11 +4723,16 @@
     <mergeCell ref="I18:I21"/>
     <mergeCell ref="I23:I26"/>
     <mergeCell ref="G5:H26"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="F5:F26"/>
+    <mergeCell ref="C5:C26"/>
+    <mergeCell ref="I5:I16"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="A5:B26"/>
+    <mergeCell ref="D5:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4771,7 +4741,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD946C15-825B-4BE7-A8B4-0C1FA4B1BA8B}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -4780,7 +4750,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1">
+    <row r="1" spans="1:4" ht="15.75" thickBot="1">
       <c r="A1" s="11" t="s">
         <v>22</v>
       </c>
@@ -4794,7 +4764,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="21" customHeight="1">
+    <row r="2" spans="1:4" ht="21" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -4805,7 +4775,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
@@ -4819,7 +4789,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -4830,7 +4800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
@@ -4840,9 +4810,8 @@
       <c r="C5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F5"/>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -4852,7 +4821,6 @@
       <c r="C6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5455,23 +5423,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="51" customHeight="1">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="83"/>
+      <c r="C2" s="90"/>
       <c r="D2" s="14" t="s">
         <v>37</v>
       </c>
@@ -5486,10 +5454,10 @@
       <c r="A3" s="15">
         <v>1</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="91" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="85"/>
+      <c r="C3" s="92"/>
       <c r="D3" s="16" t="s">
         <v>109</v>
       </c>
@@ -5504,10 +5472,10 @@
       <c r="A4" s="41">
         <v>2</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="86"/>
+      <c r="C4" s="83"/>
       <c r="D4" s="42" t="s">
         <v>112</v>
       </c>
@@ -5520,10 +5488,10 @@
       <c r="A5" s="41">
         <v>3</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="88"/>
+      <c r="C5" s="94"/>
       <c r="D5" s="42" t="s">
         <v>115</v>
       </c>
@@ -5536,10 +5504,10 @@
       <c r="A6" s="41">
         <v>4</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="79"/>
+      <c r="C6" s="85"/>
       <c r="D6" s="42" t="s">
         <v>117</v>
       </c>
@@ -5554,10 +5522,10 @@
       <c r="A7" s="41">
         <v>5</v>
       </c>
-      <c r="B7" s="79" t="s">
+      <c r="B7" s="85" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="79"/>
+      <c r="C7" s="85"/>
       <c r="D7" t="s">
         <v>120</v>
       </c>
@@ -5570,10 +5538,10 @@
       <c r="A8" s="41">
         <v>6</v>
       </c>
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="90"/>
+      <c r="C8" s="86"/>
       <c r="D8" t="s">
         <v>122</v>
       </c>
@@ -5586,10 +5554,10 @@
       <c r="A9" s="41">
         <v>7</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="83" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="86"/>
+      <c r="C9" s="83"/>
       <c r="D9" t="s">
         <v>124</v>
       </c>
@@ -5602,10 +5570,10 @@
       <c r="A10" s="41">
         <v>8</v>
       </c>
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="79" t="s">
         <v>125</v>
       </c>
-      <c r="C10" s="89"/>
+      <c r="C10" s="79"/>
       <c r="D10" s="45"/>
       <c r="E10" s="43" t="s">
         <v>126</v>
@@ -5618,10 +5586,10 @@
       <c r="A11" s="41">
         <v>9</v>
       </c>
-      <c r="B11" s="89" t="s">
+      <c r="B11" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="C11" s="89"/>
+      <c r="C11" s="79"/>
       <c r="D11"/>
       <c r="E11" s="43" t="s">
         <v>126</v>
@@ -5634,10 +5602,10 @@
       <c r="A12" s="41">
         <v>10</v>
       </c>
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="83" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="86"/>
+      <c r="C12" s="83"/>
       <c r="D12"/>
       <c r="E12" s="43" t="s">
         <v>126</v>
@@ -5650,10 +5618,10 @@
       <c r="A13" s="41">
         <v>11</v>
       </c>
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="83" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="86"/>
+      <c r="C13" s="83"/>
       <c r="D13"/>
       <c r="E13" s="43" t="s">
         <v>126</v>
@@ -5666,10 +5634,10 @@
       <c r="A14" s="41">
         <v>12</v>
       </c>
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="79" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="89"/>
+      <c r="C14" s="79"/>
       <c r="D14" t="s">
         <v>135</v>
       </c>
@@ -5684,10 +5652,10 @@
       <c r="A15" s="41">
         <v>13</v>
       </c>
-      <c r="B15" s="89" t="s">
+      <c r="B15" s="79" t="s">
         <v>137</v>
       </c>
-      <c r="C15" s="89"/>
+      <c r="C15" s="79"/>
       <c r="D15" t="s">
         <v>138</v>
       </c>
@@ -5702,10 +5670,10 @@
       <c r="A16" s="41">
         <v>14</v>
       </c>
-      <c r="B16" s="89" t="s">
+      <c r="B16" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="89"/>
+      <c r="C16" s="79"/>
       <c r="D16"/>
       <c r="E16" s="43" t="s">
         <v>126</v>
@@ -5718,10 +5686,10 @@
       <c r="A17" s="41">
         <v>15</v>
       </c>
-      <c r="B17" s="89" t="s">
+      <c r="B17" s="79" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="89"/>
+      <c r="C17" s="79"/>
       <c r="D17"/>
       <c r="E17" s="43" t="s">
         <v>126</v>
@@ -5734,10 +5702,10 @@
       <c r="A18" s="41">
         <v>16</v>
       </c>
-      <c r="B18" s="89" t="s">
+      <c r="B18" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="C18" s="89"/>
+      <c r="C18" s="79"/>
       <c r="D18" t="s">
         <v>145</v>
       </c>
@@ -5752,10 +5720,10 @@
       <c r="A19" s="41">
         <v>17</v>
       </c>
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="C19" s="89"/>
+      <c r="C19" s="79"/>
       <c r="D19"/>
       <c r="E19" s="43" t="s">
         <v>126</v>
@@ -5768,10 +5736,10 @@
       <c r="A20" s="41">
         <v>18</v>
       </c>
-      <c r="B20" s="89" t="s">
+      <c r="B20" s="79" t="s">
         <v>149</v>
       </c>
-      <c r="C20" s="89"/>
+      <c r="C20" s="79"/>
       <c r="D20"/>
       <c r="E20" s="43" t="s">
         <v>126</v>
@@ -5784,10 +5752,10 @@
       <c r="A21" s="41">
         <v>19</v>
       </c>
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="79" t="s">
         <v>151</v>
       </c>
-      <c r="C21" s="89"/>
+      <c r="C21" s="79"/>
       <c r="D21" s="18" t="s">
         <v>152</v>
       </c>
@@ -5802,10 +5770,10 @@
       <c r="A22" s="46">
         <v>20</v>
       </c>
-      <c r="B22" s="89" t="s">
+      <c r="B22" s="79" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="89"/>
+      <c r="C22" s="79"/>
       <c r="D22" s="18"/>
       <c r="E22" s="43" t="s">
         <v>126</v>
@@ -5818,10 +5786,10 @@
       <c r="A23" s="46">
         <v>21</v>
       </c>
-      <c r="B23" s="89" t="s">
+      <c r="B23" s="79" t="s">
         <v>156</v>
       </c>
-      <c r="C23" s="89"/>
+      <c r="C23" s="79"/>
       <c r="D23" s="18"/>
       <c r="E23" s="43" t="s">
         <v>126</v>
@@ -5834,10 +5802,10 @@
       <c r="A24" s="46">
         <v>22</v>
       </c>
-      <c r="B24" s="86" t="s">
+      <c r="B24" s="83" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="86"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="18" t="s">
         <v>159</v>
       </c>
@@ -5852,10 +5820,10 @@
       <c r="A25" s="46">
         <v>23</v>
       </c>
-      <c r="B25" s="89" t="s">
+      <c r="B25" s="79" t="s">
         <v>162</v>
       </c>
-      <c r="C25" s="89"/>
+      <c r="C25" s="79"/>
       <c r="D25" s="18"/>
       <c r="E25" s="43" t="s">
         <v>126</v>
@@ -5866,10 +5834,10 @@
       <c r="A26" s="46">
         <v>24</v>
       </c>
-      <c r="B26" s="89" t="s">
+      <c r="B26" s="79" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="89"/>
+      <c r="C26" s="79"/>
       <c r="D26" s="18"/>
       <c r="E26" s="43" t="s">
         <v>126</v>
@@ -5880,10 +5848,10 @@
       <c r="A27" s="46">
         <v>25</v>
       </c>
-      <c r="B27" s="91" t="s">
+      <c r="B27" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="C27" s="91"/>
+      <c r="C27" s="84"/>
       <c r="D27" s="18" t="s">
         <v>165</v>
       </c>
@@ -5898,10 +5866,10 @@
       <c r="A28" s="46">
         <v>26</v>
       </c>
-      <c r="B28" s="89" t="s">
+      <c r="B28" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="C28" s="89"/>
+      <c r="C28" s="79"/>
       <c r="D28" s="18"/>
       <c r="E28" s="43" t="s">
         <v>126</v>
@@ -5914,10 +5882,10 @@
       <c r="A29" s="46">
         <v>27</v>
       </c>
-      <c r="B29" s="89" t="s">
+      <c r="B29" s="79" t="s">
         <v>169</v>
       </c>
-      <c r="C29" s="89"/>
+      <c r="C29" s="79"/>
       <c r="D29" s="18"/>
       <c r="E29" s="43" t="s">
         <v>126</v>
@@ -5930,10 +5898,10 @@
       <c r="A30" s="46">
         <v>28</v>
       </c>
-      <c r="B30" s="86" t="s">
+      <c r="B30" s="83" t="s">
         <v>171</v>
       </c>
-      <c r="C30" s="86"/>
+      <c r="C30" s="83"/>
       <c r="D30" s="18" t="s">
         <v>172</v>
       </c>
@@ -5948,10 +5916,10 @@
       <c r="A31" s="46">
         <v>29</v>
       </c>
-      <c r="B31" s="89" t="s">
+      <c r="B31" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="89"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="18"/>
       <c r="E31" s="43" t="s">
         <v>126</v>
@@ -5964,10 +5932,10 @@
       <c r="A32" s="46">
         <v>30</v>
       </c>
-      <c r="B32" s="89" t="s">
+      <c r="B32" s="79" t="s">
         <v>176</v>
       </c>
-      <c r="C32" s="89"/>
+      <c r="C32" s="79"/>
       <c r="D32" s="18"/>
       <c r="E32" s="43" t="s">
         <v>126</v>
@@ -5980,10 +5948,10 @@
       <c r="A33" s="46">
         <v>31</v>
       </c>
-      <c r="B33" s="89" t="s">
+      <c r="B33" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="C33" s="89"/>
+      <c r="C33" s="79"/>
       <c r="D33" s="18"/>
       <c r="E33" s="43" t="s">
         <v>126</v>
@@ -5996,10 +5964,10 @@
       <c r="A34" s="46">
         <v>32</v>
       </c>
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="83" t="s">
         <v>180</v>
       </c>
-      <c r="C34" s="86"/>
+      <c r="C34" s="83"/>
       <c r="D34" s="18"/>
       <c r="E34" s="43" t="s">
         <v>126</v>
@@ -6012,10 +5980,10 @@
       <c r="A35" s="46">
         <v>33</v>
       </c>
-      <c r="B35" s="89" t="s">
+      <c r="B35" s="79" t="s">
         <v>182</v>
       </c>
-      <c r="C35" s="89"/>
+      <c r="C35" s="79"/>
       <c r="D35" s="18" t="s">
         <v>183</v>
       </c>
@@ -6030,10 +5998,10 @@
       <c r="A36" s="46">
         <v>34</v>
       </c>
-      <c r="B36" s="89" t="s">
+      <c r="B36" s="79" t="s">
         <v>185</v>
       </c>
-      <c r="C36" s="89"/>
+      <c r="C36" s="79"/>
       <c r="D36" s="18" t="s">
         <v>186</v>
       </c>
@@ -6048,10 +6016,10 @@
       <c r="A37" s="46">
         <v>35</v>
       </c>
-      <c r="B37" s="89" t="s">
+      <c r="B37" s="79" t="s">
         <v>188</v>
       </c>
-      <c r="C37" s="89"/>
+      <c r="C37" s="79"/>
       <c r="D37" s="18" t="s">
         <v>135</v>
       </c>
@@ -6081,14 +6049,14 @@
       <c r="F39" s="34"/>
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A40" s="92" t="s">
+      <c r="A40" s="80" t="s">
         <v>192</v>
       </c>
-      <c r="B40" s="93"/>
-      <c r="C40" s="93"/>
-      <c r="D40" s="93"/>
-      <c r="E40" s="93"/>
-      <c r="F40" s="94"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="82"/>
     </row>
     <row r="41" spans="1:6" ht="18.75" customHeight="1">
       <c r="A41" s="36" t="s">
@@ -6728,14 +6696,24 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
@@ -6748,30 +6726,30 @@
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -6943,16 +6921,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6963,11 +6931,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF69206-D903-4973-BD90-FEDD12C88DA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B079ADB8-D386-4C38-9FD3-437EE2FC6D11}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B079ADB8-D386-4C38-9FD3-437EE2FC6D11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDF69206-D903-4973-BD90-FEDD12C88DA5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
